--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO_Pretty.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO_Pretty.xlsx
@@ -7543,7 +7543,7 @@
     <row r="126">
       <c r="A126" s="47" t="inlineStr">
         <is>
-          <t>BGSR02101725</t>
+          <t>BGSR02102163-01</t>
         </is>
       </c>
       <c r="B126" s="23" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="130">
       <c r="A130" s="47" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>BGSR02102163-02</t>
         </is>
       </c>
       <c r="B130" s="23" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="133">
       <c r="A133" s="42" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>BGSR02102163-03</t>
         </is>
       </c>
       <c r="B133" s="30" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="158">
       <c r="A158" s="36" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>SRSR10101834</t>
         </is>
       </c>
       <c r="B158" s="29" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="165">
       <c r="A165" s="47" t="inlineStr">
         <is>
-          <t>SRSR10103460-09</t>
+          <t>BGSR02102163-04</t>
         </is>
       </c>
       <c r="B165" s="23" t="inlineStr">
@@ -18253,7 +18253,7 @@
     <row r="336">
       <c r="A336" s="36" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>BGSR02102163-05</t>
         </is>
       </c>
       <c r="B336" s="29" t="inlineStr">

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO_Pretty.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO_Pretty.xlsx
@@ -424,10 +424,10 @@
     <xf numFmtId="0" fontId="25" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="25" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -853,17 +853,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>316</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>670</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>38  / 30</t>
+          <t>33  / 30</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="C17" s="22" t="n">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="F17" s="22" t="n">
-        <v>627</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C18" s="24" t="n">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="E18" s="25" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>114</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="F19" s="28" t="n">
-        <v>817</v>
+        <v>670</v>
       </c>
     </row>
     <row r="21">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C23" s="28" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="C24" s="31" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="C25" s="28" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="C26" s="20" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
@@ -1107,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1195,7 +1195,7 @@
     <row r="2">
       <c r="A2" s="36" t="inlineStr">
         <is>
-          <t>SRSR10105860-01</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B2" s="29" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="3">
       <c r="A3" s="42" t="inlineStr">
         <is>
-          <t>BGBG02022104-01</t>
+          <t>BGBG02022104</t>
         </is>
       </c>
       <c r="B3" s="30" t="inlineStr">
@@ -1297,114 +1297,114 @@
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t>BGBG02022104-04</t>
+          <t>BGSR02102118</t>
         </is>
       </c>
       <c r="B4" s="29" t="inlineStr">
         <is>
-          <t>Parimpora to Budgam</t>
-        </is>
-      </c>
-      <c r="C4" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Parimpora to Hazratbal</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D4" s="38" t="n">
-        <v>22.663</v>
+        <v>16.104</v>
       </c>
       <c r="E4" s="39" t="inlineStr">
         <is>
           <t>Peri_Urban</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+      <c r="F4" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G4" s="41" t="n">
         <v>35</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>113.3</v>
+        <v>80.5</v>
       </c>
       <c r="I4" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" s="41" t="n">
-        <v>57658</v>
+        <v>113789</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="42" t="inlineStr">
         <is>
-          <t>BGSR02102118-01</t>
+          <t>BGBG02022106</t>
         </is>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Hazratbal</t>
-        </is>
-      </c>
-      <c r="C5" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Parimpora to Chadora</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D5" s="43" t="n">
-        <v>16.104</v>
+        <v>25.752</v>
       </c>
       <c r="E5" s="44" t="inlineStr">
         <is>
           <t>Peri_Urban</t>
         </is>
       </c>
-      <c r="F5" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F5" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G5" s="46" t="n">
         <v>35</v>
       </c>
       <c r="H5" s="43" t="n">
-        <v>80.5</v>
+        <v>128.8</v>
       </c>
       <c r="I5" s="46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="46" t="n">
-        <v>113789</v>
+        <v>137879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="36" t="inlineStr">
         <is>
-          <t>BGBG02022106-01</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>Parimpora to Chadora</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
@@ -1413,23 +1413,23 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>25.752</v>
+        <v>9.308</v>
       </c>
       <c r="E6" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F6" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G6" s="41" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>128.8</v>
+        <v>74.5</v>
       </c>
       <c r="I6" s="41" t="n">
         <v>5</v>
@@ -1444,18 +1444,18 @@
         <v>0</v>
       </c>
       <c r="M6" s="41" t="n">
-        <v>137879</v>
+        <v>90006</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="42" t="inlineStr">
         <is>
-          <t>SRSR10103460-01</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Lalbazar to LD</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C7" s="37" t="inlineStr">
@@ -1464,49 +1464,49 @@
         </is>
       </c>
       <c r="D7" s="43" t="n">
-        <v>9.308</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E7" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F7" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F7" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G7" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H7" s="43" t="n">
-        <v>74.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I7" s="46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" s="46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" s="46" t="n">
-        <v>90006</v>
+        <v>34248</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="36" t="inlineStr">
         <is>
-          <t>SRGB10055804-01</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>Soura to Ganderbal</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
@@ -1515,100 +1515,100 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.859999999999999</v>
+        <v>8.433</v>
       </c>
       <c r="E8" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F8" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G8" s="41" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H8" s="38" t="n">
-        <v>78.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="I8" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L8" s="41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="41" t="n">
-        <v>34248</v>
+        <v>83040</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="42" t="inlineStr">
         <is>
-          <t>SRSR10103462-01</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Lalbazar to Lalchowk</t>
-        </is>
-      </c>
-      <c r="C9" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Soura to Hazratbal</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D9" s="43" t="n">
-        <v>8.433</v>
+        <v>8.337</v>
       </c>
       <c r="E9" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F9" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F9" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G9" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H9" s="43" t="n">
-        <v>67.5</v>
+        <v>66.7</v>
       </c>
       <c r="I9" s="46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="46" t="n">
-        <v>83040</v>
+        <v>59647</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="36" t="inlineStr">
         <is>
-          <t>SRSR10105860-02</t>
+          <t>SRSR10105218</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Soura to LD</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
@@ -1617,26 +1617,26 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>10.817</v>
+        <v>8.127000000000001</v>
       </c>
       <c r="E10" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F10" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G10" s="41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H10" s="38" t="n">
-        <v>86.5</v>
+        <v>65</v>
       </c>
       <c r="I10" s="41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J10" s="41" t="n">
         <v>0</v>
@@ -1645,30 +1645,30 @@
         <v>0</v>
       </c>
       <c r="L10" s="41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M10" s="41" t="n">
-        <v>85889</v>
+        <v>59483</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="42" t="inlineStr">
         <is>
-          <t>SRSR10105818-01</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>Soura to Hazratbal</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Hazratbal to LD</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D11" s="43" t="n">
-        <v>8.337</v>
+        <v>9.286</v>
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
@@ -1684,33 +1684,33 @@
         <v>35</v>
       </c>
       <c r="H11" s="43" t="n">
-        <v>66.7</v>
+        <v>74.3</v>
       </c>
       <c r="I11" s="46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="46" t="n">
-        <v>59647</v>
+        <v>72103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>SRSR10105218-01</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>TRC to Hazratbal</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
@@ -1719,11 +1719,11 @@
         </is>
       </c>
       <c r="D12" s="38" t="n">
-        <v>8.127000000000001</v>
+        <v>18.799</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="F12" s="48" t="inlineStr">
@@ -1735,33 +1735,33 @@
         <v>35</v>
       </c>
       <c r="H12" s="38" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="I12" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" s="41" t="n">
-        <v>59483</v>
+        <v>117138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="42" t="inlineStr">
         <is>
-          <t>SRSR10101860-01</t>
+          <t>SRSR10106360</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>Hazratbal to LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="C13" s="37" t="inlineStr">
@@ -1770,100 +1770,100 @@
         </is>
       </c>
       <c r="D13" s="43" t="n">
-        <v>9.286</v>
+        <v>9.178000000000001</v>
       </c>
       <c r="E13" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F13" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G13" s="46" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H13" s="43" t="n">
-        <v>74.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="46" t="n">
-        <v>72103</v>
+        <v>88125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>SRAN10015813-01</t>
+          <t>BGSR02102161</t>
         </is>
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>Soura to Railway Station</t>
-        </is>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Parimpora to Saidakadal</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D14" s="38" t="n">
-        <v>18.799</v>
+        <v>14.067</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F14" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G14" s="41" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H14" s="38" t="n">
-        <v>94</v>
+        <v>112.5</v>
       </c>
       <c r="I14" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="J14" s="41" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="41" t="n">
-        <v>117138</v>
+        <v>116598</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>SRSR10106360-01</t>
+          <t>BGSR02102140</t>
         </is>
       </c>
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>Malbagh to LD</t>
+          <t>Parimpora to Pantha Chowk</t>
         </is>
       </c>
       <c r="C15" s="37" t="inlineStr">
@@ -1872,23 +1872,23 @@
         </is>
       </c>
       <c r="D15" s="43" t="n">
-        <v>9.178000000000001</v>
+        <v>21.307</v>
       </c>
       <c r="E15" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F15" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F15" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G15" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H15" s="43" t="n">
-        <v>73.40000000000001</v>
+        <v>106.5</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>5</v>
@@ -1897,75 +1897,75 @@
         <v>0</v>
       </c>
       <c r="K15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="L15" s="46" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" s="46" t="n">
-        <v>88125</v>
+        <v>133241</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102161-01</t>
+          <t>BGSR02102143</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>Parimpora to Saidakadal</t>
-        </is>
-      </c>
-      <c r="C16" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Parimpora to Rawalpora</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D16" s="38" t="n">
-        <v>14.067</v>
+        <v>14.409</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F16" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F16" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G16" s="41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H16" s="38" t="n">
-        <v>112.5</v>
+        <v>115.3</v>
       </c>
       <c r="I16" s="41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J16" s="41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" s="41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L16" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="41" t="n">
-        <v>116598</v>
+        <v>97796</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="42" t="inlineStr">
         <is>
-          <t>BGSR02102140-01</t>
+          <t>SRSR10103406</t>
         </is>
       </c>
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Pantha Chowk</t>
+          <t>Lalbazar to Qamarwari</t>
         </is>
       </c>
       <c r="C17" s="37" t="inlineStr">
@@ -1974,23 +1974,23 @@
         </is>
       </c>
       <c r="D17" s="43" t="n">
-        <v>21.307</v>
+        <v>8.695</v>
       </c>
       <c r="E17" s="44" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F17" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G17" s="46" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H17" s="43" t="n">
-        <v>106.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>5</v>
@@ -1999,24 +1999,24 @@
         <v>0</v>
       </c>
       <c r="K17" s="46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L17" s="46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M17" s="46" t="n">
-        <v>133241</v>
+        <v>83258</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="36" t="inlineStr">
         <is>
-          <t>SRAN10015813-02</t>
+          <t>SRSR10104446</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Soura to Railway Station</t>
+          <t>Safakadal to SMHS</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
@@ -2025,26 +2025,26 @@
         </is>
       </c>
       <c r="D18" s="38" t="n">
-        <v>18.412</v>
+        <v>1.579</v>
       </c>
       <c r="E18" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F18" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G18" s="41" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H18" s="38" t="n">
-        <v>92.09999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J18" s="41" t="n">
         <v>0</v>
@@ -2053,46 +2053,46 @@
         <v>0</v>
       </c>
       <c r="L18" s="41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M18" s="41" t="n">
-        <v>117708</v>
+        <v>18965</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="42" t="inlineStr">
         <is>
-          <t>BGSR02102143-01</t>
+          <t>SRSR10105846</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Rawalpora</t>
-        </is>
-      </c>
-      <c r="C19" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Soura to SMHS</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D19" s="43" t="n">
-        <v>14.409</v>
+        <v>7.687</v>
       </c>
       <c r="E19" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F19" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G19" s="46" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H19" s="43" t="n">
-        <v>115.3</v>
+        <v>61.5</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>5</v>
@@ -2107,18 +2107,18 @@
         <v>0</v>
       </c>
       <c r="M19" s="46" t="n">
-        <v>97796</v>
+        <v>75598</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102143-03</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>Parimpora to Rawalpora</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="D20" s="38" t="n">
-        <v>14.409</v>
+        <v>12.845</v>
       </c>
       <c r="E20" s="39" t="inlineStr">
         <is>
@@ -2143,84 +2143,84 @@
         <v>35</v>
       </c>
       <c r="H20" s="38" t="n">
-        <v>115.3</v>
+        <v>102.8</v>
       </c>
       <c r="I20" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" s="41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M20" s="41" t="n">
-        <v>97796</v>
+        <v>102944</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="42" t="inlineStr">
         <is>
-          <t>SRSR10103406</t>
+          <t>SRSR10105806</t>
         </is>
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>Lalbazar to Qamarwari</t>
-        </is>
-      </c>
-      <c r="C21" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Soura to Qamarwari</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D21" s="43" t="n">
-        <v>8.695</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E21" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F21" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F21" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G21" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H21" s="43" t="n">
-        <v>69.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I21" s="46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="46" t="n">
-        <v>83258</v>
+        <v>63584</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="36" t="inlineStr">
         <is>
-          <t>SRSR10104446-01</t>
+          <t>SRSP10090619</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>Safakadal to SMHS</t>
+          <t>Qamarwari to Pathachowk</t>
         </is>
       </c>
       <c r="C22" s="37" t="inlineStr">
@@ -2229,58 +2229,58 @@
         </is>
       </c>
       <c r="D22" s="38" t="n">
-        <v>1.579</v>
+        <v>19.719</v>
       </c>
       <c r="E22" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F22" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F22" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G22" s="41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H22" s="38" t="n">
-        <v>12.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I22" s="41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="41" t="n">
-        <v>18965</v>
+        <v>122169</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="42" t="inlineStr">
         <is>
-          <t>SRSR10105846-01</t>
+          <t>SRSR10100615</t>
         </is>
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>Soura to SMHS</t>
-        </is>
-      </c>
-      <c r="C23" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Qamarwari to Dalgate</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D23" s="43" t="n">
-        <v>7.687</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="E23" s="44" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="43" t="n">
-        <v>61.5</v>
+        <v>70.8</v>
       </c>
       <c r="I23" s="46" t="n">
         <v>5</v>
@@ -2311,18 +2311,18 @@
         <v>0</v>
       </c>
       <c r="M23" s="46" t="n">
-        <v>75598</v>
+        <v>77329</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="36" t="inlineStr">
         <is>
-          <t>SRBG10025821-02</t>
+          <t>SRBG10026121</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>Soura to Parimpora</t>
+          <t>Saidakadal to Parimpora</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
@@ -2331,58 +2331,58 @@
         </is>
       </c>
       <c r="D24" s="38" t="n">
-        <v>12.845</v>
+        <v>14.556</v>
       </c>
       <c r="E24" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F24" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G24" s="41" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H24" s="38" t="n">
-        <v>102.8</v>
+        <v>116.4</v>
       </c>
       <c r="I24" s="41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J24" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L24" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="41" t="n">
-        <v>102944</v>
+        <v>116554</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="42" t="inlineStr">
         <is>
-          <t>SRSR10105806</t>
+          <t>SRBG10023421</t>
         </is>
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>Soura to Qamarwari</t>
-        </is>
-      </c>
-      <c r="C25" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Lalbazar to Parimpora</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D25" s="43" t="n">
-        <v>9.300000000000001</v>
+        <v>12.646</v>
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>35</v>
       </c>
       <c r="H25" s="43" t="n">
-        <v>74.40000000000001</v>
+        <v>101.2</v>
       </c>
       <c r="I25" s="46" t="n">
         <v>4</v>
@@ -2413,18 +2413,18 @@
         <v>0</v>
       </c>
       <c r="M25" s="46" t="n">
-        <v>63584</v>
+        <v>100546</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="36" t="inlineStr">
         <is>
-          <t>SRSP10090619</t>
+          <t>SRSR10100618</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>Qamarwari to Pathachowk</t>
+          <t>Qamarwari to Hazratbal</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
@@ -2433,11 +2433,11 @@
         </is>
       </c>
       <c r="D26" s="38" t="n">
-        <v>19.719</v>
+        <v>14.081</v>
       </c>
       <c r="E26" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F26" s="48" t="inlineStr">
@@ -2449,33 +2449,33 @@
         <v>35</v>
       </c>
       <c r="H26" s="38" t="n">
-        <v>98.59999999999999</v>
+        <v>112.6</v>
       </c>
       <c r="I26" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="41" t="n">
-        <v>122169</v>
+        <v>102032</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100615-01</t>
+          <t>BGBG02022123</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
         <is>
-          <t>Qamarwari to Dalgate</t>
+          <t>Parimpora to Rangrath</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
@@ -2484,49 +2484,49 @@
         </is>
       </c>
       <c r="D27" s="43" t="n">
-        <v>8.843999999999999</v>
+        <v>19.812</v>
       </c>
       <c r="E27" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F27" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F27" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G27" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H27" s="43" t="n">
-        <v>70.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I27" s="46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J27" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L27" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="46" t="n">
-        <v>77329</v>
+        <v>87853</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="36" t="inlineStr">
         <is>
-          <t>SRSR10104446-02</t>
+          <t>SRGB10056102</t>
         </is>
       </c>
       <c r="B28" s="29" t="inlineStr">
         <is>
-          <t>Safakadal to SMHS</t>
+          <t>Saidakadal to Bypass</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="D28" s="38" t="n">
-        <v>1.579</v>
+        <v>13.28</v>
       </c>
       <c r="E28" s="39" t="inlineStr">
         <is>
@@ -2551,46 +2551,46 @@
         <v>20</v>
       </c>
       <c r="H28" s="38" t="n">
-        <v>12.6</v>
+        <v>106.2</v>
       </c>
       <c r="I28" s="41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J28" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M28" s="41" t="n">
-        <v>18965</v>
+        <v>108026</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="42" t="inlineStr">
         <is>
-          <t>SRBG10026121-01</t>
+          <t>SRSR10100840</t>
         </is>
       </c>
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>Saidakadal to Parimpora</t>
-        </is>
-      </c>
-      <c r="C29" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Batamallo to Pantha Chowk</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D29" s="43" t="n">
-        <v>14.556</v>
+        <v>17.436</v>
       </c>
       <c r="E29" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="F29" s="40" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="G29" s="46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H29" s="43" t="n">
-        <v>116.4</v>
+        <v>87.2</v>
       </c>
       <c r="I29" s="46" t="n">
         <v>7</v>
@@ -2617,18 +2617,18 @@
         <v>0</v>
       </c>
       <c r="M29" s="46" t="n">
-        <v>116554</v>
+        <v>92763</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="36" t="inlineStr">
         <is>
-          <t>SRBG10023421-01</t>
+          <t>SRSR10105965</t>
         </is>
       </c>
       <c r="B30" s="29" t="inlineStr">
         <is>
-          <t>Lalbazar to Parimpora</t>
+          <t>JVC to Batwara</t>
         </is>
       </c>
       <c r="C30" s="37" t="inlineStr">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="D30" s="38" t="n">
-        <v>12.646</v>
+        <v>14.66</v>
       </c>
       <c r="E30" s="39" t="inlineStr">
         <is>
@@ -2653,33 +2653,33 @@
         <v>35</v>
       </c>
       <c r="H30" s="38" t="n">
-        <v>101.2</v>
+        <v>117.3</v>
       </c>
       <c r="I30" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L30" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="41" t="n">
-        <v>100546</v>
+        <v>99772</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100618</t>
+          <t>SRSR10106040</t>
         </is>
       </c>
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>Qamarwari to Hazratbal</t>
+          <t>LD to Panthachowk</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D31" s="43" t="n">
-        <v>14.081</v>
+        <v>13.344</v>
       </c>
       <c r="E31" s="44" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>35</v>
       </c>
       <c r="H31" s="43" t="n">
-        <v>112.6</v>
+        <v>106.8</v>
       </c>
       <c r="I31" s="46" t="n">
         <v>5</v>
@@ -2719,18 +2719,18 @@
         <v>0</v>
       </c>
       <c r="M31" s="46" t="n">
-        <v>102032</v>
+        <v>78707</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="36" t="inlineStr">
         <is>
-          <t>SRBG10023421-07</t>
+          <t>SRSR10104060</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>Lalbazar to Parimpora</t>
+          <t>Panthachowk to LD</t>
         </is>
       </c>
       <c r="C32" s="37" t="inlineStr">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D32" s="38" t="n">
-        <v>12.646</v>
+        <v>12.905</v>
       </c>
       <c r="E32" s="39" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>35</v>
       </c>
       <c r="H32" s="38" t="n">
-        <v>101.2</v>
+        <v>103.2</v>
       </c>
       <c r="I32" s="41" t="n">
         <v>4</v>
@@ -2764,24 +2764,24 @@
         <v>0</v>
       </c>
       <c r="K32" s="41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L32" s="41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M32" s="41" t="n">
-        <v>100546</v>
+        <v>77073</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="42" t="inlineStr">
         <is>
-          <t>BGBG02022123-01</t>
+          <t>SRBG10022504</t>
         </is>
       </c>
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Rangrath</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr">
@@ -2790,23 +2790,23 @@
         </is>
       </c>
       <c r="D33" s="43" t="n">
-        <v>19.812</v>
+        <v>12.642</v>
       </c>
       <c r="E33" s="44" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F33" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F33" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G33" s="46" t="n">
         <v>35</v>
       </c>
       <c r="H33" s="43" t="n">
-        <v>99.09999999999999</v>
+        <v>101.1</v>
       </c>
       <c r="I33" s="46" t="n">
         <v>4</v>
@@ -2821,18 +2821,18 @@
         <v>0</v>
       </c>
       <c r="M33" s="46" t="n">
-        <v>87853</v>
+        <v>101463</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="36" t="inlineStr">
         <is>
-          <t>SRGB10056102-01</t>
+          <t>SRSR10100605</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>Saidakadal to Bypass</t>
+          <t>Qamarwari to Baghi Mehtab</t>
         </is>
       </c>
       <c r="C34" s="37" t="inlineStr">
@@ -2841,49 +2841,49 @@
         </is>
       </c>
       <c r="D34" s="38" t="n">
-        <v>13.28</v>
+        <v>13.166</v>
       </c>
       <c r="E34" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F34" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F34" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G34" s="41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H34" s="38" t="n">
-        <v>106.2</v>
+        <v>105.3</v>
       </c>
       <c r="I34" s="41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J34" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L34" s="41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M34" s="41" t="n">
-        <v>108026</v>
+        <v>88820</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="42" t="inlineStr">
         <is>
-          <t>SRGB10056102-02</t>
+          <t>SRSR10101358</t>
         </is>
       </c>
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>Saidakadal to Bypass</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="D35" s="43" t="n">
-        <v>13.28</v>
+        <v>14.108</v>
       </c>
       <c r="E35" s="44" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>20</v>
       </c>
       <c r="H35" s="43" t="n">
-        <v>106.2</v>
+        <v>105.9</v>
       </c>
       <c r="I35" s="46" t="n">
         <v>7</v>
@@ -2923,133 +2923,133 @@
         <v>0</v>
       </c>
       <c r="M35" s="46" t="n">
-        <v>108026</v>
+        <v>133070</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="36" t="inlineStr">
         <is>
-          <t>SRSR10100840-01</t>
+          <t>BGSR02102122</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>Batamallo to Pantha Chowk</t>
-        </is>
-      </c>
-      <c r="C36" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Parimpora to Humhama</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D36" s="38" t="n">
-        <v>17.436</v>
+        <v>12.759</v>
       </c>
       <c r="E36" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F36" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F36" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G36" s="41" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H36" s="38" t="n">
-        <v>87.2</v>
+        <v>89.7</v>
       </c>
       <c r="I36" s="41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J36" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L36" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="41" t="n">
-        <v>92763</v>
+        <v>78440</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100840-02</t>
+          <t>SRPW10086005</t>
         </is>
       </c>
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>Batamallo to Pantha Chowk</t>
-        </is>
-      </c>
-      <c r="C37" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>LD to Pampore</t>
+        </is>
+      </c>
+      <c r="C37" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D37" s="43" t="n">
-        <v>17.436</v>
+        <v>15.854</v>
       </c>
       <c r="E37" s="44" t="inlineStr">
         <is>
           <t>Peri_Urban</t>
         </is>
       </c>
-      <c r="F37" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F37" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G37" s="46" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H37" s="43" t="n">
-        <v>87.2</v>
+        <v>79.3</v>
       </c>
       <c r="I37" s="46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J37" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L37" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="46" t="n">
-        <v>92763</v>
+        <v>93243</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="36" t="inlineStr">
         <is>
-          <t>SRSR10100840-03</t>
+          <t>SRSR10100915</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>Batamallo to Pantha Chowk</t>
-        </is>
-      </c>
-      <c r="C38" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Batmaloo to Dalgate</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D38" s="38" t="n">
-        <v>17.436</v>
+        <v>4.792</v>
       </c>
       <c r="E38" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F38" s="40" t="inlineStr">
@@ -3058,147 +3058,147 @@
         </is>
       </c>
       <c r="G38" s="41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H38" s="38" t="n">
-        <v>87.2</v>
+        <v>38.3</v>
       </c>
       <c r="I38" s="41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J38" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L38" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="41" t="n">
-        <v>92763</v>
+        <v>42983</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100840-04</t>
+          <t>SRSR10101834</t>
         </is>
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>Batamallo to Pantha Chowk</t>
-        </is>
-      </c>
-      <c r="C39" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Hazratbal, Lalbazar</t>
+        </is>
+      </c>
+      <c r="C39" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D39" s="43" t="n">
-        <v>13.366</v>
+        <v>8.808</v>
       </c>
       <c r="E39" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F39" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F39" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G39" s="46" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H39" s="43" t="n">
-        <v>101.8</v>
+        <v>70.5</v>
       </c>
       <c r="I39" s="46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J39" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L39" s="46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M39" s="46" t="n">
-        <v>84840</v>
+        <v>72765</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="36" t="inlineStr">
         <is>
-          <t>SRSR10100840-05</t>
+          <t>SRBG10026021</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Batamallo to Pantha Chowk</t>
-        </is>
-      </c>
-      <c r="C40" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>LD to Parimpora</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D40" s="38" t="n">
-        <v>13.366</v>
+        <v>7.761</v>
       </c>
       <c r="E40" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F40" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F40" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G40" s="41" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H40" s="38" t="n">
-        <v>101.8</v>
+        <v>62.1</v>
       </c>
       <c r="I40" s="41" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J40" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="41" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L40" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="41" t="n">
-        <v>84840</v>
+        <v>60135</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100840-06</t>
+          <t>SRSR10105815</t>
         </is>
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>Batamallo to Pantha Chowk</t>
-        </is>
-      </c>
-      <c r="C41" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
+          <t>Soura to Dalgate</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
         </is>
       </c>
       <c r="D41" s="43" t="n">
-        <v>13.366</v>
+        <v>11.745</v>
       </c>
       <c r="E41" s="44" t="inlineStr">
         <is>
@@ -3211,87 +3211,87 @@
         </is>
       </c>
       <c r="G41" s="46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H41" s="43" t="n">
-        <v>101.8</v>
+        <v>94</v>
       </c>
       <c r="I41" s="46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J41" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L41" s="46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M41" s="46" t="n">
-        <v>84840</v>
+        <v>93551</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102140-04</t>
+          <t>SRSR10105808</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>Parimpora to Panthachowk</t>
-        </is>
-      </c>
-      <c r="C42" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Soura to Batamallo</t>
+        </is>
+      </c>
+      <c r="C42" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D42" s="38" t="n">
-        <v>21.307</v>
+        <v>9.167</v>
       </c>
       <c r="E42" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F42" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G42" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H42" s="38" t="n">
-        <v>106.5</v>
+        <v>73.3</v>
       </c>
       <c r="I42" s="41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="41" t="n">
-        <v>133241</v>
+        <v>94361</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100840-07</t>
+          <t>BGSR02102258</t>
         </is>
       </c>
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>Batamallo to Panthachok</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="C43" s="37" t="inlineStr">
@@ -3300,49 +3300,49 @@
         </is>
       </c>
       <c r="D43" s="43" t="n">
-        <v>17.988</v>
+        <v>22.053</v>
       </c>
       <c r="E43" s="44" t="inlineStr">
         <is>
           <t>Peri_Urban</t>
         </is>
       </c>
-      <c r="F43" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+      <c r="F43" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G43" s="46" t="n">
         <v>35</v>
       </c>
       <c r="H43" s="43" t="n">
-        <v>89.90000000000001</v>
+        <v>110.3</v>
       </c>
       <c r="I43" s="46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J43" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="46" t="n">
-        <v>97927</v>
+        <v>115477</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="36" t="inlineStr">
         <is>
-          <t>SRSR10105965</t>
+          <t>SRBG10026004</t>
         </is>
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>JVC to Batwara</t>
+          <t>LD to Budgam</t>
         </is>
       </c>
       <c r="C44" s="37" t="inlineStr">
@@ -3351,11 +3351,11 @@
         </is>
       </c>
       <c r="D44" s="38" t="n">
-        <v>14.66</v>
+        <v>21.784</v>
       </c>
       <c r="E44" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="F44" s="48" t="inlineStr">
@@ -3367,7 +3367,7 @@
         <v>35</v>
       </c>
       <c r="H44" s="38" t="n">
-        <v>117.3</v>
+        <v>108.9</v>
       </c>
       <c r="I44" s="41" t="n">
         <v>5</v>
@@ -3382,18 +3382,18 @@
         <v>0</v>
       </c>
       <c r="M44" s="41" t="n">
-        <v>99772</v>
+        <v>72180</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="42" t="inlineStr">
         <is>
-          <t>SRSR10106040-01</t>
+          <t>BGPW02082105</t>
         </is>
       </c>
       <c r="B45" s="30" t="inlineStr">
         <is>
-          <t>LD to Panthachowk</t>
+          <t>Parimpora to Pampore</t>
         </is>
       </c>
       <c r="C45" s="37" t="inlineStr">
@@ -3402,11 +3402,11 @@
         </is>
       </c>
       <c r="D45" s="43" t="n">
-        <v>13.344</v>
+        <v>23.817</v>
       </c>
       <c r="E45" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="F45" s="48" t="inlineStr">
@@ -3418,7 +3418,7 @@
         <v>35</v>
       </c>
       <c r="H45" s="43" t="n">
-        <v>106.8</v>
+        <v>119.1</v>
       </c>
       <c r="I45" s="46" t="n">
         <v>5</v>
@@ -3433,18 +3433,18 @@
         <v>0</v>
       </c>
       <c r="M45" s="46" t="n">
-        <v>78707</v>
+        <v>148103</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="36" t="inlineStr">
         <is>
-          <t>SRSR10104060-01</t>
+          <t>BGSR02102215</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>Panthachowk to LD</t>
+          <t>Rangpora to Dalgate</t>
         </is>
       </c>
       <c r="C46" s="37" t="inlineStr">
@@ -3453,49 +3453,49 @@
         </is>
       </c>
       <c r="D46" s="38" t="n">
-        <v>12.905</v>
+        <v>15.533</v>
       </c>
       <c r="E46" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F46" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G46" s="41" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H46" s="38" t="n">
-        <v>103.2</v>
+        <v>77.7</v>
       </c>
       <c r="I46" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L46" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="41" t="n">
-        <v>77073</v>
+        <v>120044</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="42" t="inlineStr">
         <is>
-          <t>SRBG10022504</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B47" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Jawahairnagar</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C47" s="37" t="inlineStr">
@@ -3504,49 +3504,49 @@
         </is>
       </c>
       <c r="D47" s="43" t="n">
-        <v>12.642</v>
+        <v>13.983</v>
       </c>
       <c r="E47" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F47" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G47" s="46" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H47" s="43" t="n">
-        <v>101.1</v>
+        <v>111.7</v>
       </c>
       <c r="I47" s="46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J47" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L47" s="46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M47" s="46" t="n">
-        <v>101463</v>
+        <v>118930</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="36" t="inlineStr">
         <is>
-          <t>SRSR10100615-06</t>
+          <t>SRBG10020621</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>Qamarwari to Dalgate</t>
+          <t>Qamarwari to Parimpora</t>
         </is>
       </c>
       <c r="C48" s="37" t="inlineStr">
@@ -3555,23 +3555,23 @@
         </is>
       </c>
       <c r="D48" s="38" t="n">
-        <v>8.843999999999999</v>
+        <v>14.577</v>
       </c>
       <c r="E48" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F48" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F48" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G48" s="41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H48" s="38" t="n">
-        <v>70.8</v>
+        <v>116.6</v>
       </c>
       <c r="I48" s="41" t="n">
         <v>5</v>
@@ -3580,24 +3580,24 @@
         <v>0</v>
       </c>
       <c r="K48" s="41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" s="41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M48" s="41" t="n">
-        <v>77329</v>
+        <v>71580</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100605</t>
+          <t>SRSR10106444</t>
         </is>
       </c>
       <c r="B49" s="30" t="inlineStr">
         <is>
-          <t>Qamarwari to Baghi Mehtab</t>
+          <t>Ma Road to Safakadal</t>
         </is>
       </c>
       <c r="C49" s="37" t="inlineStr">
@@ -3606,49 +3606,49 @@
         </is>
       </c>
       <c r="D49" s="43" t="n">
-        <v>13.166</v>
+        <v>11.432</v>
       </c>
       <c r="E49" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F49" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G49" s="46" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H49" s="43" t="n">
-        <v>105.3</v>
+        <v>91.5</v>
       </c>
       <c r="I49" s="46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J49" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L49" s="46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M49" s="46" t="n">
-        <v>88820</v>
+        <v>83691</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102163-03</t>
+          <t>BGSR02102260</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>Parimpora to Jawahirnagar</t>
+          <t>Rangpora to LD</t>
         </is>
       </c>
       <c r="C50" s="37" t="inlineStr">
@@ -3657,49 +3657,49 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>12.642</v>
+        <v>10.925</v>
       </c>
       <c r="E50" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F50" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G50" s="41" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H50" s="38" t="n">
-        <v>101.1</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I50" s="41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J50" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L50" s="41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M50" s="41" t="n">
-        <v>101463</v>
+        <v>97167</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="42" t="inlineStr">
         <is>
-          <t>SRSR10101358-01</t>
+          <t>SRSR10105862</t>
         </is>
       </c>
       <c r="B51" s="30" t="inlineStr">
         <is>
-          <t>Chanapora to Soura</t>
+          <t>Soura to Lalchowk</t>
         </is>
       </c>
       <c r="C51" s="37" t="inlineStr">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="D51" s="43" t="n">
-        <v>14.108</v>
+        <v>9.494</v>
       </c>
       <c r="E51" s="44" t="inlineStr">
         <is>
@@ -3724,33 +3724,33 @@
         <v>20</v>
       </c>
       <c r="H51" s="43" t="n">
-        <v>105.9</v>
+        <v>76</v>
       </c>
       <c r="I51" s="46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J51" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L51" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="46" t="n">
-        <v>133070</v>
+        <v>86195</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102122-01</t>
+          <t>SRBG10026421</t>
         </is>
       </c>
       <c r="B52" s="29" t="inlineStr">
         <is>
-          <t>Parimpora to Humhama</t>
+          <t>Ma Road to Parimpora</t>
         </is>
       </c>
       <c r="C52" s="37" t="inlineStr">
@@ -3759,11 +3759,11 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>12.759</v>
+        <v>18.669</v>
       </c>
       <c r="E52" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="F52" s="48" t="inlineStr">
@@ -3775,7 +3775,7 @@
         <v>35</v>
       </c>
       <c r="H52" s="38" t="n">
-        <v>89.7</v>
+        <v>93.3</v>
       </c>
       <c r="I52" s="41" t="n">
         <v>4</v>
@@ -3790,18 +3790,18 @@
         <v>0</v>
       </c>
       <c r="M52" s="41" t="n">
-        <v>78440</v>
+        <v>117830</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="42" t="inlineStr">
         <is>
-          <t>SRGB10055804-03</t>
+          <t>SRPW10085110</t>
         </is>
       </c>
       <c r="B53" s="30" t="inlineStr">
         <is>
-          <t>Soura to Ganderbal</t>
+          <t>Srinagar to Ratnipora</t>
         </is>
       </c>
       <c r="C53" s="37" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="D53" s="43" t="n">
-        <v>9.859999999999999</v>
+        <v>25.567</v>
       </c>
       <c r="E53" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="F53" s="45" t="inlineStr">
@@ -3826,84 +3826,84 @@
         <v>35</v>
       </c>
       <c r="H53" s="43" t="n">
-        <v>78.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="I53" s="46" t="n">
         <v>4</v>
       </c>
       <c r="J53" s="46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" s="46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L53" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M53" s="46" t="n">
-        <v>34248</v>
+        <v>65466</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="36" t="inlineStr">
         <is>
-          <t>SRPW10086005-01</t>
+          <t>SRBG10025129</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>LD to Pampore</t>
-        </is>
-      </c>
-      <c r="C54" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D54" s="38" t="n">
-        <v>15.854</v>
+          <t>Srinagar to Tangmarg</t>
+        </is>
+      </c>
+      <c r="C54" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D54" s="49" t="n">
+        <v>40.568</v>
       </c>
       <c r="E54" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F54" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G54" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H54" s="38" t="n">
-        <v>79.3</v>
+        <v>121.7</v>
       </c>
       <c r="I54" s="41" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J54" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="41" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L54" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M54" s="41" t="n">
-        <v>93243</v>
+        <v>191399</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100915</t>
+          <t>SRSP10095110</t>
         </is>
       </c>
       <c r="B55" s="30" t="inlineStr">
         <is>
-          <t>Batmaloo to Dalgate</t>
+          <t>Srinagar to Hajin</t>
         </is>
       </c>
       <c r="C55" s="37" t="inlineStr">
@@ -3911,30 +3911,30 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D55" s="43" t="n">
-        <v>4.792</v>
+      <c r="D55" s="50" t="n">
+        <v>35.566</v>
       </c>
       <c r="E55" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F55" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F55" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G55" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H55" s="43" t="n">
-        <v>38.3</v>
+        <v>106.7</v>
       </c>
       <c r="I55" s="46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" s="46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K55" s="46" t="n">
         <v>3</v>
@@ -3943,18 +3943,18 @@
         <v>0</v>
       </c>
       <c r="M55" s="46" t="n">
-        <v>42983</v>
+        <v>123517</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="36" t="inlineStr">
         <is>
-          <t>SRSR10103462-03</t>
+          <t>SRPW10085114</t>
         </is>
       </c>
       <c r="B56" s="29" t="inlineStr">
         <is>
-          <t>Lalbazar to Lalchowk</t>
+          <t>Srinagar to Tral Nowdal</t>
         </is>
       </c>
       <c r="C56" s="37" t="inlineStr">
@@ -3962,50 +3962,50 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D56" s="38" t="n">
-        <v>8.433</v>
+      <c r="D56" s="49" t="n">
+        <v>39.5</v>
       </c>
       <c r="E56" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F56" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F56" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G56" s="41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H56" s="38" t="n">
-        <v>67.5</v>
+        <v>118.5</v>
       </c>
       <c r="I56" s="41" t="n">
         <v>5</v>
       </c>
       <c r="J56" s="41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" s="41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M56" s="41" t="n">
-        <v>83040</v>
+        <v>83195</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="42" t="inlineStr">
         <is>
-          <t>SRSR10101860-17</t>
+          <t>SRAN10015112</t>
         </is>
       </c>
       <c r="B57" s="30" t="inlineStr">
         <is>
-          <t>Hazratbal to LD</t>
+          <t>Srinagar to Qazigund</t>
         </is>
       </c>
       <c r="C57" s="37" t="inlineStr">
@@ -4013,50 +4013,50 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D57" s="43" t="n">
-        <v>8.250999999999999</v>
+      <c r="D57" s="50" t="n">
+        <v>71.01900000000001</v>
       </c>
       <c r="E57" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F57" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F57" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G57" s="46" t="n">
         <v>35</v>
       </c>
       <c r="H57" s="43" t="n">
-        <v>66</v>
+        <v>213.1</v>
       </c>
       <c r="I57" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="J57" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="J57" s="46" t="n">
-        <v>0</v>
-      </c>
       <c r="K57" s="46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L57" s="46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M57" s="46" t="n">
-        <v>55948</v>
+        <v>114863</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="36" t="inlineStr">
         <is>
-          <t>SRSR10101834</t>
+          <t>BPSR03100151</t>
         </is>
       </c>
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>Hazratbal, Lalbazar</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="C58" s="37" t="inlineStr">
@@ -4064,50 +4064,50 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D58" s="38" t="n">
-        <v>8.808</v>
+      <c r="D58" s="49" t="n">
+        <v>58.597</v>
       </c>
       <c r="E58" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F58" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F58" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G58" s="41" t="n">
         <v>35</v>
       </c>
       <c r="H58" s="38" t="n">
-        <v>70.5</v>
+        <v>175.8</v>
       </c>
       <c r="I58" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="J58" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="J58" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="41" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" s="41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M58" s="41" t="n">
-        <v>72765</v>
+        <v>152803</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="42" t="inlineStr">
         <is>
-          <t>BGSR02102122-03</t>
+          <t>BPSR03100158</t>
         </is>
       </c>
       <c r="B59" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Humhama</t>
+          <t>Bandipora to Soura</t>
         </is>
       </c>
       <c r="C59" s="37" t="inlineStr">
@@ -4115,50 +4115,50 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D59" s="43" t="n">
-        <v>12.759</v>
+      <c r="D59" s="50" t="n">
+        <v>51.094</v>
       </c>
       <c r="E59" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F59" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F59" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G59" s="46" t="n">
         <v>35</v>
       </c>
       <c r="H59" s="43" t="n">
-        <v>89.7</v>
+        <v>153.3</v>
       </c>
       <c r="I59" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="J59" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="J59" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="46" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" s="46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M59" s="46" t="n">
-        <v>78440</v>
+        <v>110656</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="36" t="inlineStr">
         <is>
-          <t>SRBG10026021-01</t>
+          <t>SRSR10104951</t>
         </is>
       </c>
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>LD to Parimpora</t>
+          <t>Sopore to Srinagar</t>
         </is>
       </c>
       <c r="C60" s="37" t="inlineStr">
@@ -4166,50 +4166,50 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D60" s="38" t="n">
-        <v>7.761</v>
+      <c r="D60" s="49" t="n">
+        <v>50.022</v>
       </c>
       <c r="E60" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F60" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F60" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G60" s="41" t="n">
         <v>35</v>
       </c>
       <c r="H60" s="38" t="n">
-        <v>62.1</v>
+        <v>150.1</v>
       </c>
       <c r="I60" s="41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J60" s="41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K60" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="41" t="n">
-        <v>60135</v>
+        <v>173791</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="42" t="inlineStr">
         <is>
-          <t>SRSR10105815</t>
+          <t>SPSR09102451</t>
         </is>
       </c>
       <c r="B61" s="30" t="inlineStr">
         <is>
-          <t>Soura to Dalgate</t>
+          <t>Shopian to Srinagar</t>
         </is>
       </c>
       <c r="C61" s="37" t="inlineStr">
@@ -4217,101 +4217,101 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D61" s="43" t="n">
-        <v>11.745</v>
+      <c r="D61" s="50" t="n">
+        <v>48.367</v>
       </c>
       <c r="E61" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F61" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F61" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G61" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H61" s="43" t="n">
-        <v>94</v>
+        <v>145.1</v>
       </c>
       <c r="I61" s="46" t="n">
         <v>6</v>
       </c>
       <c r="J61" s="46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" s="46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L61" s="46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M61" s="46" t="n">
-        <v>93551</v>
+        <v>154407</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="36" t="inlineStr">
         <is>
-          <t>SRSR10105808</t>
+          <t>SRSR10103151</t>
         </is>
       </c>
       <c r="B62" s="29" t="inlineStr">
         <is>
-          <t>Soura to Batamallo</t>
-        </is>
-      </c>
-      <c r="C62" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D62" s="38" t="n">
-        <v>9.167</v>
+          <t>Kulgam to Srinagar</t>
+        </is>
+      </c>
+      <c r="C62" s="37" t="inlineStr">
+        <is>
+          <t>Retained as Feeder</t>
+        </is>
+      </c>
+      <c r="D62" s="49" t="n">
+        <v>67.01900000000001</v>
       </c>
       <c r="E62" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F62" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F62" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G62" s="41" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H62" s="38" t="n">
-        <v>73.3</v>
+        <v>201.1</v>
       </c>
       <c r="I62" s="41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J62" s="41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K62" s="41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L62" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="41" t="n">
-        <v>94361</v>
+        <v>113085</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="42" t="inlineStr">
         <is>
-          <t>BGSR02102258-01</t>
+          <t>SRSR10105751</t>
         </is>
       </c>
       <c r="B63" s="30" t="inlineStr">
         <is>
-          <t>Rangpora to Soura</t>
+          <t>Yaripora to Srinagar</t>
         </is>
       </c>
       <c r="C63" s="37" t="inlineStr">
@@ -4319,50 +4319,50 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D63" s="43" t="n">
-        <v>22.053</v>
+      <c r="D63" s="50" t="n">
+        <v>64.929</v>
       </c>
       <c r="E63" s="44" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F63" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F63" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G63" s="46" t="n">
         <v>35</v>
       </c>
       <c r="H63" s="43" t="n">
-        <v>110.3</v>
+        <v>194.8</v>
       </c>
       <c r="I63" s="46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J63" s="46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K63" s="46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L63" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="46" t="n">
-        <v>115477</v>
+        <v>105224</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="36" t="inlineStr">
         <is>
-          <t>SRBG10026004-01</t>
+          <t>PWSR08100851</t>
         </is>
       </c>
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>LD to Budgam</t>
+          <t>Pulwama to Srinagar</t>
         </is>
       </c>
       <c r="C64" s="37" t="inlineStr">
@@ -4371,49 +4371,49 @@
         </is>
       </c>
       <c r="D64" s="38" t="n">
-        <v>21.784</v>
+        <v>28.043</v>
       </c>
       <c r="E64" s="39" t="inlineStr">
         <is>
           <t>Peri_Urban</t>
         </is>
       </c>
-      <c r="F64" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F64" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G64" s="41" t="n">
         <v>35</v>
       </c>
       <c r="H64" s="38" t="n">
-        <v>108.9</v>
+        <v>140.2</v>
       </c>
       <c r="I64" s="41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J64" s="41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L64" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M64" s="41" t="n">
-        <v>72180</v>
+        <v>117099</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="42" t="inlineStr">
         <is>
-          <t>BGPW02082105-01</t>
+          <t>SRPW10085102</t>
         </is>
       </c>
       <c r="B65" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Pampore</t>
+          <t>Srinagar to Khrew</t>
         </is>
       </c>
       <c r="C65" s="37" t="inlineStr">
@@ -4422,62 +4422,62 @@
         </is>
       </c>
       <c r="D65" s="43" t="n">
-        <v>23.817</v>
+        <v>19.597</v>
       </c>
       <c r="E65" s="44" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F65" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F65" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G65" s="46" t="n">
         <v>35</v>
       </c>
       <c r="H65" s="43" t="n">
-        <v>119.1</v>
+        <v>156.8</v>
       </c>
       <c r="I65" s="46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J65" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L65" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M65" s="46" t="n">
-        <v>148103</v>
+        <v>75685</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102215</t>
+          <t>SRAN10015113</t>
         </is>
       </c>
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>Rangpora to Dalgate</t>
-        </is>
-      </c>
-      <c r="C66" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Srinagar to Railway</t>
+        </is>
+      </c>
+      <c r="C66" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D66" s="38" t="n">
-        <v>15.533</v>
+        <v>7.778</v>
       </c>
       <c r="E66" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F66" s="40" t="inlineStr">
@@ -4489,33 +4489,33 @@
         <v>20</v>
       </c>
       <c r="H66" s="38" t="n">
-        <v>77.7</v>
+        <v>55.3</v>
       </c>
       <c r="I66" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J66" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L66" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M66" s="41" t="n">
-        <v>120044</v>
+        <v>73036</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100840-23</t>
+          <t>SRGB10055102</t>
         </is>
       </c>
       <c r="B67" s="30" t="inlineStr">
         <is>
-          <t>Batamallo to Panthachowk</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C67" s="37" t="inlineStr">
@@ -4524,49 +4524,49 @@
         </is>
       </c>
       <c r="D67" s="43" t="n">
-        <v>17.436</v>
+        <v>8.340999999999999</v>
       </c>
       <c r="E67" s="44" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F67" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F67" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G67" s="46" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H67" s="43" t="n">
-        <v>87.2</v>
+        <v>66.7</v>
       </c>
       <c r="I67" s="46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J67" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67" s="46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M67" s="46" t="n">
-        <v>92763</v>
+        <v>68065</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102262-01</t>
+          <t>SRSR10105111</t>
         </is>
       </c>
       <c r="B68" s="29" t="inlineStr">
         <is>
-          <t>Rangpora to Lalchowk</t>
+          <t>Srinagar to Buchpora</t>
         </is>
       </c>
       <c r="C68" s="37" t="inlineStr">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D68" s="38" t="n">
-        <v>13.983</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E68" s="39" t="inlineStr">
         <is>
@@ -4591,33 +4591,33 @@
         <v>20</v>
       </c>
       <c r="H68" s="38" t="n">
-        <v>111.7</v>
+        <v>75</v>
       </c>
       <c r="I68" s="41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J68" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L68" s="41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M68" s="41" t="n">
-        <v>118930</v>
+        <v>89823</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="42" t="inlineStr">
         <is>
-          <t>BGSR02102262-03</t>
+          <t>SRPW10085105</t>
         </is>
       </c>
       <c r="B69" s="30" t="inlineStr">
         <is>
-          <t>Rangpora to Lalchowk</t>
+          <t>Srinagar to Pampore</t>
         </is>
       </c>
       <c r="C69" s="37" t="inlineStr">
@@ -4626,49 +4626,49 @@
         </is>
       </c>
       <c r="D69" s="43" t="n">
-        <v>13.983</v>
+        <v>12.883</v>
       </c>
       <c r="E69" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F69" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F69" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G69" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H69" s="43" t="n">
-        <v>111.7</v>
+        <v>80.8</v>
       </c>
       <c r="I69" s="46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J69" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L69" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M69" s="46" t="n">
-        <v>118930</v>
+        <v>70093</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="36" t="inlineStr">
         <is>
-          <t>BGPW02082105-02</t>
+          <t>SRBG10025104</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Parimpora to Pampore</t>
+          <t>Srinagar to Budgam</t>
         </is>
       </c>
       <c r="C70" s="37" t="inlineStr">
@@ -4677,49 +4677,49 @@
         </is>
       </c>
       <c r="D70" s="38" t="n">
-        <v>23.817</v>
+        <v>23.639</v>
       </c>
       <c r="E70" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F70" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F70" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G70" s="41" t="n">
         <v>35</v>
       </c>
       <c r="H70" s="38" t="n">
-        <v>119.1</v>
+        <v>189.1</v>
       </c>
       <c r="I70" s="41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J70" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L70" s="41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M70" s="41" t="n">
-        <v>148103</v>
+        <v>88926</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="42" t="inlineStr">
         <is>
-          <t>SRSR10106360-02</t>
+          <t>SRBG10025110</t>
         </is>
       </c>
       <c r="B71" s="30" t="inlineStr">
         <is>
-          <t>Malbagh to LD</t>
+          <t>Srinagar to Gund</t>
         </is>
       </c>
       <c r="C71" s="37" t="inlineStr">
@@ -4727,63 +4727,63 @@
           <t>Retained as Feeder</t>
         </is>
       </c>
-      <c r="D71" s="43" t="n">
-        <v>9.178000000000001</v>
+      <c r="D71" s="50" t="n">
+        <v>57.421</v>
       </c>
       <c r="E71" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F71" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F71" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G71" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H71" s="43" t="n">
-        <v>73.40000000000001</v>
+        <v>287.1</v>
       </c>
       <c r="I71" s="46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J71" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="46" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L71" s="46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M71" s="46" t="n">
-        <v>88125</v>
+        <v>173998</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="36" t="inlineStr">
         <is>
-          <t>SRPW10086005-16</t>
+          <t>SRBG10025105</t>
         </is>
       </c>
       <c r="B72" s="29" t="inlineStr">
         <is>
-          <t>LD to Pampore</t>
-        </is>
-      </c>
-      <c r="C72" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Srinagar to Chadoora</t>
+        </is>
+      </c>
+      <c r="C72" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D72" s="38" t="n">
-        <v>15.854</v>
+        <v>16.895</v>
       </c>
       <c r="E72" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F72" s="48" t="inlineStr">
@@ -4795,33 +4795,33 @@
         <v>35</v>
       </c>
       <c r="H72" s="38" t="n">
-        <v>79.3</v>
+        <v>135.2</v>
       </c>
       <c r="I72" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J72" s="41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K72" s="41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M72" s="41" t="n">
-        <v>93243</v>
+        <v>108893</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="42" t="inlineStr">
         <is>
-          <t>SRBG10020621-01</t>
+          <t>SRBR10045106</t>
         </is>
       </c>
       <c r="B73" s="30" t="inlineStr">
         <is>
-          <t>Qamarwari to Parimpora</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="C73" s="37" t="inlineStr">
@@ -4830,23 +4830,23 @@
         </is>
       </c>
       <c r="D73" s="43" t="n">
-        <v>14.577</v>
+        <v>16.558</v>
       </c>
       <c r="E73" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F73" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F73" s="45" t="inlineStr">
+        <is>
+          <t>LP</t>
         </is>
       </c>
       <c r="G73" s="46" t="n">
         <v>35</v>
       </c>
       <c r="H73" s="43" t="n">
-        <v>116.6</v>
+        <v>125.9</v>
       </c>
       <c r="I73" s="46" t="n">
         <v>5</v>
@@ -4861,18 +4861,18 @@
         <v>0</v>
       </c>
       <c r="M73" s="46" t="n">
-        <v>71580</v>
+        <v>71141</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="36" t="inlineStr">
         <is>
-          <t>SRBG10020621-04</t>
+          <t>SRGB10055104</t>
         </is>
       </c>
       <c r="B74" s="29" t="inlineStr">
         <is>
-          <t>Qamarwari to Parimpora</t>
+          <t>Srinagar to Ganderbal</t>
         </is>
       </c>
       <c r="C74" s="37" t="inlineStr">
@@ -4881,11 +4881,11 @@
         </is>
       </c>
       <c r="D74" s="38" t="n">
-        <v>20.044</v>
+        <v>16.689</v>
       </c>
       <c r="E74" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F74" s="48" t="inlineStr">
@@ -4897,33 +4897,33 @@
         <v>35</v>
       </c>
       <c r="H74" s="38" t="n">
-        <v>100.2</v>
+        <v>133.5</v>
       </c>
       <c r="I74" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K74" s="41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L74" s="41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M74" s="41" t="n">
-        <v>95364</v>
+        <v>102776</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="42" t="inlineStr">
         <is>
-          <t>SRSR10106444</t>
+          <t>SRSR10105102</t>
         </is>
       </c>
       <c r="B75" s="30" t="inlineStr">
         <is>
-          <t>Ma Road to Safakadal</t>
+          <t>TRC Srinagar to Airport</t>
         </is>
       </c>
       <c r="C75" s="37" t="inlineStr">
@@ -4932,62 +4932,62 @@
         </is>
       </c>
       <c r="D75" s="43" t="n">
-        <v>11.432</v>
+        <v>14.524</v>
       </c>
       <c r="E75" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F75" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
+      <c r="F75" s="48" t="inlineStr">
+        <is>
+          <t>MP</t>
         </is>
       </c>
       <c r="G75" s="46" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H75" s="43" t="n">
-        <v>91.5</v>
+        <v>116.2</v>
       </c>
       <c r="I75" s="46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J75" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K75" s="46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L75" s="46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M75" s="46" t="n">
-        <v>83691</v>
+        <v>96198</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102260</t>
+          <t>BGBR02042106</t>
         </is>
       </c>
       <c r="B76" s="29" t="inlineStr">
         <is>
-          <t>Rangpora to LD</t>
-        </is>
-      </c>
-      <c r="C76" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Parimpora to Harwan via Brein Nishat</t>
+        </is>
+      </c>
+      <c r="C76" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D76" s="38" t="n">
-        <v>10.925</v>
+        <v>23.249</v>
       </c>
       <c r="E76" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="F76" s="40" t="inlineStr">
@@ -4996,45 +4996,45 @@
         </is>
       </c>
       <c r="G76" s="41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H76" s="38" t="n">
-        <v>87.40000000000001</v>
+        <v>116.2</v>
       </c>
       <c r="I76" s="41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J76" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K76" s="41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L76" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M76" s="41" t="n">
-        <v>97167</v>
+        <v>170188</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="42" t="inlineStr">
         <is>
-          <t>SRSR10105862-01</t>
+          <t>SRSR10100808-01</t>
         </is>
       </c>
       <c r="B77" s="30" t="inlineStr">
         <is>
-          <t>Soura to Lalchowk</t>
-        </is>
-      </c>
-      <c r="C77" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Batamaloo to Nasrullah Pora via Jehangir Chowk Rambagh Hyderpora</t>
+        </is>
+      </c>
+      <c r="C77" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D77" s="43" t="n">
-        <v>9.494</v>
+        <v>7.083</v>
       </c>
       <c r="E77" s="44" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="G77" s="46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H77" s="43" t="n">
-        <v>76</v>
+        <v>43.4</v>
       </c>
       <c r="I77" s="46" t="n">
         <v>5</v>
@@ -5065,273 +5065,273 @@
         <v>0</v>
       </c>
       <c r="M77" s="46" t="n">
-        <v>86195</v>
+        <v>33298</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="36" t="inlineStr">
         <is>
-          <t>SRBG10026421</t>
+          <t>SRSR10100918</t>
         </is>
       </c>
       <c r="B78" s="29" t="inlineStr">
         <is>
-          <t>Ma Road to Parimpora</t>
-        </is>
-      </c>
-      <c r="C78" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Batamaloo to Hazratbal via Khanyar</t>
+        </is>
+      </c>
+      <c r="C78" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D78" s="38" t="n">
-        <v>18.669</v>
+        <v>12.926</v>
       </c>
       <c r="E78" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F78" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F78" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G78" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H78" s="38" t="n">
-        <v>93.3</v>
+        <v>103.4</v>
       </c>
       <c r="I78" s="41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J78" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L78" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="41" t="n">
-        <v>117830</v>
+        <v>98975</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="42" t="inlineStr">
         <is>
-          <t>SRSR10105218-02</t>
+          <t>SRBG10020905</t>
         </is>
       </c>
       <c r="B79" s="30" t="inlineStr">
         <is>
-          <t>TRC to Hazratbal</t>
-        </is>
-      </c>
-      <c r="C79" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Batamaloo to Chadoora Chowk via Jehangir Chowk</t>
+        </is>
+      </c>
+      <c r="C79" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D79" s="43" t="n">
-        <v>8.127000000000001</v>
+        <v>10.858</v>
       </c>
       <c r="E79" s="44" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F79" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F79" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G79" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H79" s="43" t="n">
-        <v>65</v>
+        <v>65.8</v>
       </c>
       <c r="I79" s="46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J79" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K79" s="46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L79" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M79" s="46" t="n">
-        <v>59483</v>
+        <v>39417</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="36" t="inlineStr">
         <is>
-          <t>SRBG10026021-07</t>
+          <t>SRSR10106039</t>
         </is>
       </c>
       <c r="B80" s="29" t="inlineStr">
         <is>
-          <t>LD to Parimpora</t>
-        </is>
-      </c>
-      <c r="C80" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>LD Hospital to Pandach via Jehangir Chowk Dalgate Khanyar</t>
+        </is>
+      </c>
+      <c r="C80" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D80" s="38" t="n">
-        <v>7.761</v>
+        <v>10.884</v>
       </c>
       <c r="E80" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F80" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F80" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G80" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H80" s="38" t="n">
-        <v>62.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I80" s="41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J80" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K80" s="41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L80" s="41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M80" s="41" t="n">
-        <v>60135</v>
+        <v>96645</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="42" t="inlineStr">
         <is>
-          <t>BGSR02102163-05</t>
+          <t>SRBG10024017</t>
         </is>
       </c>
       <c r="B81" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Jawahirnagar</t>
-        </is>
-      </c>
-      <c r="C81" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Pantha Chowk to Narbal Crossing via Sonwar Jehangir Chowk Qamarwari</t>
+        </is>
+      </c>
+      <c r="C81" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D81" s="43" t="n">
-        <v>12.642</v>
+        <v>19.752</v>
       </c>
       <c r="E81" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F81" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F81" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G81" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H81" s="43" t="n">
-        <v>101.1</v>
+        <v>98.8</v>
       </c>
       <c r="I81" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="J81" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="J81" s="46" t="n">
-        <v>0</v>
-      </c>
       <c r="K81" s="46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L81" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="46" t="n">
-        <v>101463</v>
+        <v>101613</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="36" t="inlineStr">
         <is>
-          <t>SRPW10085110</t>
+          <t>SRPW10080908</t>
         </is>
       </c>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>Srinagar to Ratnipora</t>
-        </is>
-      </c>
-      <c r="C82" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D82" s="38" t="n">
-        <v>25.567</v>
+          <t>Batamaloo to Drussu Pulwama via Marwal</t>
+        </is>
+      </c>
+      <c r="C82" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D82" s="49" t="n">
+        <v>32.735</v>
       </c>
       <c r="E82" s="39" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F82" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F82" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G82" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H82" s="38" t="n">
-        <v>76.7</v>
+        <v>163.7</v>
       </c>
       <c r="I82" s="41" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J82" s="41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K82" s="41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L82" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="41" t="n">
-        <v>65466</v>
+        <v>119785</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="42" t="inlineStr">
         <is>
-          <t>SRBG10025129</t>
+          <t>SRBG10020904-01</t>
         </is>
       </c>
       <c r="B83" s="30" t="inlineStr">
         <is>
-          <t>Srinagar to Tangmarg</t>
+          <t>Batamaloo to Budgam Railway Station via Khumeni Chowk</t>
         </is>
       </c>
       <c r="C83" s="47" t="inlineStr">
@@ -5339,12 +5339,12 @@
           <t>Upgraded to Trunk</t>
         </is>
       </c>
-      <c r="D83" s="49" t="n">
-        <v>40.568</v>
+      <c r="D83" s="43" t="n">
+        <v>15.685</v>
       </c>
       <c r="E83" s="44" t="inlineStr">
         <is>
-          <t>Regional_District</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="F83" s="40" t="inlineStr">
@@ -5356,472 +5356,472 @@
         <v>15</v>
       </c>
       <c r="H83" s="43" t="n">
-        <v>121.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I83" s="46" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J83" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K83" s="46" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L83" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="46" t="n">
-        <v>191399</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="36" t="inlineStr">
         <is>
-          <t>SRSP10095110</t>
+          <t>SRSR10105418</t>
         </is>
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>Srinagar to Hajin</t>
-        </is>
-      </c>
-      <c r="C84" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D84" s="50" t="n">
-        <v>35.566</v>
+          <t>Parimpora to Naseem Bagh via Noorbagh Gojwara Mill Stop</t>
+        </is>
+      </c>
+      <c r="C84" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D84" s="38" t="n">
+        <v>15.058</v>
       </c>
       <c r="E84" s="39" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F84" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F84" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G84" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H84" s="38" t="n">
-        <v>106.7</v>
+        <v>75.3</v>
       </c>
       <c r="I84" s="41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J84" s="41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" s="41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L84" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="41" t="n">
-        <v>123517</v>
+        <v>114293</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="42" t="inlineStr">
         <is>
-          <t>SRPW10085114</t>
+          <t>SRBG10024005</t>
         </is>
       </c>
       <c r="B85" s="30" t="inlineStr">
         <is>
-          <t>Srinagar to Tral Nowdal</t>
-        </is>
-      </c>
-      <c r="C85" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D85" s="49" t="n">
-        <v>39.5</v>
+          <t>Pantha Chowk to Agri Kalan Kanihama via Bypass</t>
+        </is>
+      </c>
+      <c r="C85" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="n">
+        <v>23.59</v>
       </c>
       <c r="E85" s="44" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F85" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F85" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G85" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H85" s="43" t="n">
-        <v>118.5</v>
+        <v>118</v>
       </c>
       <c r="I85" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="J85" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="J85" s="46" t="n">
-        <v>2</v>
-      </c>
       <c r="K85" s="46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L85" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M85" s="46" t="n">
-        <v>83195</v>
+        <v>111959</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="36" t="inlineStr">
         <is>
-          <t>SRAN10015112</t>
+          <t>SRSR10104242</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
         <is>
-          <t>Srinagar to Qazigund</t>
-        </is>
-      </c>
-      <c r="C86" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D86" s="50" t="n">
-        <v>71.01900000000001</v>
+          <t>Old City Loop Downtown Srinagar</t>
+        </is>
+      </c>
+      <c r="C86" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D86" s="38" t="n">
+        <v>1.169</v>
       </c>
       <c r="E86" s="39" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F86" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F86" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G86" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H86" s="38" t="n">
-        <v>213.1</v>
+        <v>9.4</v>
       </c>
       <c r="I86" s="41" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J86" s="41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K86" s="41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L86" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M86" s="41" t="n">
-        <v>114863</v>
+        <v>17652</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="42" t="inlineStr">
         <is>
-          <t>BPSR03100151-01</t>
+          <t>BGSR02102451</t>
         </is>
       </c>
       <c r="B87" s="30" t="inlineStr">
         <is>
-          <t>Bandipora to Srinagar</t>
-        </is>
-      </c>
-      <c r="C87" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D87" s="49" t="n">
-        <v>58.597</v>
+          <t>Rangreth to District Court Srinagar via Barzulla Jehangir Chowk</t>
+        </is>
+      </c>
+      <c r="C87" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="n">
+        <v>10.327</v>
       </c>
       <c r="E87" s="44" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F87" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F87" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G87" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H87" s="43" t="n">
-        <v>175.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I87" s="46" t="n">
         <v>7</v>
       </c>
       <c r="J87" s="46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K87" s="46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L87" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M87" s="46" t="n">
-        <v>152803</v>
+        <v>94458</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="36" t="inlineStr">
         <is>
-          <t>BPSR03100158</t>
+          <t>SRGB10050904</t>
         </is>
       </c>
       <c r="B88" s="29" t="inlineStr">
         <is>
-          <t>Bandipora to Soura</t>
-        </is>
-      </c>
-      <c r="C88" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D88" s="50" t="n">
-        <v>51.094</v>
+          <t>Batamaloo to Beehama Ganderbal via Hazratbal Zakura</t>
+        </is>
+      </c>
+      <c r="C88" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D88" s="38" t="n">
+        <v>26.584</v>
       </c>
       <c r="E88" s="39" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F88" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F88" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G88" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H88" s="38" t="n">
-        <v>153.3</v>
+        <v>132.9</v>
       </c>
       <c r="I88" s="41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J88" s="41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K88" s="41" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L88" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="41" t="n">
-        <v>110656</v>
+        <v>152128</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="42" t="inlineStr">
         <is>
-          <t>SRSR10104951-01</t>
+          <t>SRGB10055204</t>
         </is>
       </c>
       <c r="B89" s="30" t="inlineStr">
         <is>
-          <t>Sopore to Srinagar</t>
-        </is>
-      </c>
-      <c r="C89" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D89" s="49" t="n">
-        <v>50.022</v>
+          <t>TRC to Central University Ganderbal via Karan Nagar Zoonimar 90ft Road</t>
+        </is>
+      </c>
+      <c r="C89" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D89" s="43" t="n">
+        <v>27.314</v>
       </c>
       <c r="E89" s="44" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F89" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F89" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G89" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H89" s="43" t="n">
-        <v>150.1</v>
+        <v>136.6</v>
       </c>
       <c r="I89" s="46" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J89" s="46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K89" s="46" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L89" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M89" s="46" t="n">
-        <v>173791</v>
+        <v>125528</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="36" t="inlineStr">
         <is>
-          <t>SPSR09102451</t>
+          <t>SRPW10085208</t>
         </is>
       </c>
       <c r="B90" s="29" t="inlineStr">
         <is>
-          <t>Shopian to Srinagar</t>
-        </is>
-      </c>
-      <c r="C90" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D90" s="50" t="n">
-        <v>48.367</v>
+          <t>TRC to Pulwama via Nowgam Kaanipora</t>
+        </is>
+      </c>
+      <c r="C90" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D90" s="38" t="n">
+        <v>29.364</v>
       </c>
       <c r="E90" s="39" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F90" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F90" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G90" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H90" s="38" t="n">
-        <v>145.1</v>
+        <v>146.8</v>
       </c>
       <c r="I90" s="41" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J90" s="41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K90" s="41" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L90" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M90" s="41" t="n">
-        <v>154407</v>
+        <v>127759</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="42" t="inlineStr">
         <is>
-          <t>SRSR10103151</t>
+          <t>SRSR10100808-02</t>
         </is>
       </c>
       <c r="B91" s="30" t="inlineStr">
         <is>
-          <t>Kulgam to Srinagar</t>
-        </is>
-      </c>
-      <c r="C91" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D91" s="49" t="n">
-        <v>67.01900000000001</v>
+          <t>Batamaloo Circular via Khonmoh</t>
+        </is>
+      </c>
+      <c r="C91" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D91" s="43" t="n">
+        <v>13.87</v>
       </c>
       <c r="E91" s="44" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F91" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F91" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G91" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H91" s="43" t="n">
-        <v>201.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I91" s="46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J91" s="46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K91" s="46" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L91" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M91" s="46" t="n">
-        <v>113085</v>
+        <v>81554</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="36" t="inlineStr">
         <is>
-          <t>SRSR10105751</t>
+          <t>SRAN10010902</t>
         </is>
       </c>
       <c r="B92" s="29" t="inlineStr">
         <is>
-          <t>Yaripora to Srinagar</t>
-        </is>
-      </c>
-      <c r="C92" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D92" s="50" t="n">
-        <v>64.929</v>
+          <t>Batamaloo to Womens College Batpora via Rainawari</t>
+        </is>
+      </c>
+      <c r="C92" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D92" s="38" t="n">
+        <v>4.508</v>
       </c>
       <c r="E92" s="39" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F92" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="F92" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G92" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H92" s="38" t="n">
-        <v>194.8</v>
+        <v>36.1</v>
       </c>
       <c r="I92" s="41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J92" s="41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" s="41" t="n">
         <v>4</v>
@@ -5830,120 +5830,120 @@
         <v>0</v>
       </c>
       <c r="M92" s="41" t="n">
-        <v>105224</v>
+        <v>42363</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="42" t="inlineStr">
         <is>
-          <t>PWSR08100851-01</t>
+          <t>SRBG10022505</t>
         </is>
       </c>
       <c r="B93" s="30" t="inlineStr">
         <is>
-          <t>Pulwama to Srinagar</t>
-        </is>
-      </c>
-      <c r="C93" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Jkpdc Jehangir Chowk to Wadwan</t>
+        </is>
+      </c>
+      <c r="C93" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D93" s="43" t="n">
-        <v>28.043</v>
+        <v>15.202</v>
       </c>
       <c r="E93" s="44" t="inlineStr">
         <is>
           <t>Peri_Urban</t>
         </is>
       </c>
-      <c r="F93" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+      <c r="F93" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G93" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H93" s="43" t="n">
-        <v>140.2</v>
+        <v>76</v>
       </c>
       <c r="I93" s="46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J93" s="46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K93" s="46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L93" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M93" s="46" t="n">
-        <v>117099</v>
+        <v>87331</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="36" t="inlineStr">
         <is>
-          <t>SRPW10085102-01</t>
+          <t>SRGB10054007</t>
         </is>
       </c>
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>Srinagar to Khrew</t>
-        </is>
-      </c>
-      <c r="C94" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D94" s="38" t="n">
-        <v>19.597</v>
+          <t>Pantha Chowk to Sumbal</t>
+        </is>
+      </c>
+      <c r="C94" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D94" s="49" t="n">
+        <v>35.736</v>
       </c>
       <c r="E94" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F94" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F94" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G94" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H94" s="38" t="n">
-        <v>156.8</v>
+        <v>178.7</v>
       </c>
       <c r="I94" s="41" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J94" s="41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K94" s="41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L94" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M94" s="41" t="n">
-        <v>75685</v>
+        <v>119919</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="42" t="inlineStr">
         <is>
-          <t>SRAN10015113-01</t>
+          <t>SRGB10054006</t>
         </is>
       </c>
       <c r="B95" s="30" t="inlineStr">
         <is>
-          <t>Srinagar to Railway</t>
+          <t>Pantha Chowk to Safapora</t>
         </is>
       </c>
       <c r="C95" s="47" t="inlineStr">
@@ -5951,12 +5951,12 @@
           <t>Upgraded to Trunk</t>
         </is>
       </c>
-      <c r="D95" s="43" t="n">
-        <v>7.778</v>
+      <c r="D95" s="50" t="n">
+        <v>60.631</v>
       </c>
       <c r="E95" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="F95" s="40" t="inlineStr">
@@ -5965,45 +5965,45 @@
         </is>
       </c>
       <c r="G95" s="46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H95" s="43" t="n">
-        <v>55.3</v>
+        <v>181.9</v>
       </c>
       <c r="I95" s="46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J95" s="46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K95" s="46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L95" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M95" s="46" t="n">
-        <v>73036</v>
+        <v>140491</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="36" t="inlineStr">
         <is>
-          <t>SRGB10055102-01</t>
+          <t>SRBG10020802</t>
         </is>
       </c>
       <c r="B96" s="29" t="inlineStr">
         <is>
-          <t>Srinagar to Bypass</t>
-        </is>
-      </c>
-      <c r="C96" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Batamaloo to Arath</t>
+        </is>
+      </c>
+      <c r="C96" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D96" s="38" t="n">
-        <v>8.340999999999999</v>
+        <v>12.395</v>
       </c>
       <c r="E96" s="39" t="inlineStr">
         <is>
@@ -6016,49 +6016,49 @@
         </is>
       </c>
       <c r="G96" s="41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H96" s="38" t="n">
-        <v>66.7</v>
+        <v>98.5</v>
       </c>
       <c r="I96" s="41" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J96" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K96" s="41" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L96" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="41" t="n">
-        <v>68065</v>
+        <v>73084</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="42" t="inlineStr">
         <is>
-          <t>SRSR10105111</t>
+          <t>SRPW10080902</t>
         </is>
       </c>
       <c r="B97" s="30" t="inlineStr">
         <is>
-          <t>Srinagar to Buchpora</t>
-        </is>
-      </c>
-      <c r="C97" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Batamaloo to Khrew Bus Stand</t>
+        </is>
+      </c>
+      <c r="C97" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D97" s="43" t="n">
-        <v>9.369999999999999</v>
+        <v>18.186</v>
       </c>
       <c r="E97" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="F97" s="40" t="inlineStr">
@@ -6067,163 +6067,163 @@
         </is>
       </c>
       <c r="G97" s="46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H97" s="43" t="n">
-        <v>75</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I97" s="46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J97" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K97" s="46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L97" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M97" s="46" t="n">
-        <v>89823</v>
+        <v>97093</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="36" t="inlineStr">
         <is>
-          <t>SRPW10085105-01</t>
+          <t>SRBG10020807</t>
         </is>
       </c>
       <c r="B98" s="29" t="inlineStr">
         <is>
-          <t>Srinagar to Pampore</t>
-        </is>
-      </c>
-      <c r="C98" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Batamaloo to Charesharief via Chadoora</t>
+        </is>
+      </c>
+      <c r="C98" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D98" s="38" t="n">
-        <v>12.883</v>
+        <v>29.633</v>
       </c>
       <c r="E98" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F98" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F98" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G98" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H98" s="38" t="n">
-        <v>80.8</v>
+        <v>148.2</v>
       </c>
       <c r="I98" s="41" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J98" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K98" s="41" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L98" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M98" s="41" t="n">
-        <v>70093</v>
+        <v>115125</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="42" t="inlineStr">
         <is>
-          <t>SRBG10025104-01</t>
+          <t>SRBR10044003</t>
         </is>
       </c>
       <c r="B99" s="30" t="inlineStr">
         <is>
-          <t>Srinagar to Budgam</t>
-        </is>
-      </c>
-      <c r="C99" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D99" s="43" t="n">
-        <v>23.639</v>
+          <t>Pantha Chowk to Palhalan via Sangrama Sopore</t>
+        </is>
+      </c>
+      <c r="C99" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D99" s="50" t="n">
+        <v>36.463</v>
       </c>
       <c r="E99" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F99" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F99" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G99" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H99" s="43" t="n">
-        <v>189.1</v>
+        <v>182.3</v>
       </c>
       <c r="I99" s="46" t="n">
+        <v>15</v>
+      </c>
+      <c r="J99" s="46" t="n">
         <v>7</v>
       </c>
-      <c r="J99" s="46" t="n">
-        <v>0</v>
-      </c>
       <c r="K99" s="46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L99" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M99" s="46" t="n">
-        <v>88926</v>
+        <v>131341</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="36" t="inlineStr">
         <is>
-          <t>SRBG10025110-01</t>
+          <t>SRPW10080813</t>
         </is>
       </c>
       <c r="B100" s="29" t="inlineStr">
         <is>
-          <t>Srinagar to Gund</t>
-        </is>
-      </c>
-      <c r="C100" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D100" s="50" t="n">
-        <v>57.421</v>
+          <t>Batamaloo to Dadsara Tral via Awantipora</t>
+        </is>
+      </c>
+      <c r="C100" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D100" s="49" t="n">
+        <v>43.869</v>
       </c>
       <c r="E100" s="39" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F100" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F100" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G100" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H100" s="38" t="n">
-        <v>287.1</v>
+        <v>131.6</v>
       </c>
       <c r="I100" s="41" t="n">
         <v>11</v>
@@ -6238,18 +6238,18 @@
         <v>0</v>
       </c>
       <c r="M100" s="41" t="n">
-        <v>173998</v>
+        <v>112839</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="42" t="inlineStr">
         <is>
-          <t>SRBG10025105-01</t>
+          <t>SRGB10050804-01</t>
         </is>
       </c>
       <c r="B101" s="30" t="inlineStr">
         <is>
-          <t>Srinagar to Chadoora</t>
+          <t>Batamaloo to Kangan via Hazratbal Manigam</t>
         </is>
       </c>
       <c r="C101" s="47" t="inlineStr">
@@ -6257,132 +6257,132 @@
           <t>Upgraded to Trunk</t>
         </is>
       </c>
-      <c r="D101" s="43" t="n">
-        <v>16.895</v>
+      <c r="D101" s="50" t="n">
+        <v>55.703</v>
       </c>
       <c r="E101" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F101" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F101" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G101" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H101" s="43" t="n">
-        <v>135.2</v>
+        <v>167.1</v>
       </c>
       <c r="I101" s="46" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J101" s="46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K101" s="46" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L101" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="46" t="n">
-        <v>108893</v>
+        <v>120242</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="36" t="inlineStr">
         <is>
-          <t>SRBR10045106-01</t>
+          <t>SRGB10050804-02</t>
         </is>
       </c>
       <c r="B102" s="29" t="inlineStr">
         <is>
-          <t>Srinagar to Harwan</t>
-        </is>
-      </c>
-      <c r="C102" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
-        </is>
-      </c>
-      <c r="D102" s="38" t="n">
-        <v>16.558</v>
+          <t>Batamaloo to Manigam</t>
+        </is>
+      </c>
+      <c r="C102" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
+        </is>
+      </c>
+      <c r="D102" s="49" t="n">
+        <v>54.466</v>
       </c>
       <c r="E102" s="39" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F102" s="45" t="inlineStr">
-        <is>
-          <t>LP</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="F102" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G102" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H102" s="38" t="n">
-        <v>125.9</v>
+        <v>163.4</v>
       </c>
       <c r="I102" s="41" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J102" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K102" s="41" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L102" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M102" s="41" t="n">
-        <v>71141</v>
+        <v>118108</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="42" t="inlineStr">
         <is>
-          <t>SRGB10055104</t>
+          <t>SRPW10080905</t>
         </is>
       </c>
       <c r="B103" s="30" t="inlineStr">
         <is>
-          <t>Srinagar to Ganderbal</t>
-        </is>
-      </c>
-      <c r="C103" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Batamaloo to Pinglena Pampore via Galandar</t>
+        </is>
+      </c>
+      <c r="C103" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D103" s="43" t="n">
-        <v>16.689</v>
+        <v>22.233</v>
       </c>
       <c r="E103" s="44" t="inlineStr">
         <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F103" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="F103" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G103" s="46" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H103" s="43" t="n">
-        <v>133.5</v>
+        <v>111.2</v>
       </c>
       <c r="I103" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="J103" s="46" t="n">
         <v>5</v>
-      </c>
-      <c r="J103" s="46" t="n">
-        <v>0</v>
       </c>
       <c r="K103" s="46" t="n">
         <v>5</v>
@@ -6391,69 +6391,69 @@
         <v>0</v>
       </c>
       <c r="M103" s="46" t="n">
-        <v>102776</v>
+        <v>108838</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="36" t="inlineStr">
         <is>
-          <t>SRSR10105102</t>
+          <t>SRSR10104039</t>
         </is>
       </c>
       <c r="B104" s="29" t="inlineStr">
         <is>
-          <t>TRC Srinagar to Airport</t>
-        </is>
-      </c>
-      <c r="C104" s="37" t="inlineStr">
-        <is>
-          <t>Retained as Feeder</t>
+          <t>Pantha Chowk to Panzinara</t>
+        </is>
+      </c>
+      <c r="C104" s="47" t="inlineStr">
+        <is>
+          <t>Upgraded to Trunk</t>
         </is>
       </c>
       <c r="D104" s="38" t="n">
-        <v>14.524</v>
+        <v>10.811</v>
       </c>
       <c r="E104" s="39" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="F104" s="48" t="inlineStr">
-        <is>
-          <t>MP</t>
+      <c r="F104" s="40" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="G104" s="41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H104" s="38" t="n">
-        <v>116.2</v>
+        <v>86.5</v>
       </c>
       <c r="I104" s="41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J104" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K104" s="41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L104" s="41" t="n">
         <v>0</v>
       </c>
       <c r="M104" s="41" t="n">
-        <v>96198</v>
+        <v>65968</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="42" t="inlineStr">
         <is>
-          <t>BGBR02042106</t>
+          <t>SRBG10020904-02</t>
         </is>
       </c>
       <c r="B105" s="30" t="inlineStr">
         <is>
-          <t>Parimpora to Harwan via Brein Nishat</t>
+          <t>Batamaloo to Dc Office Budgam</t>
         </is>
       </c>
       <c r="C105" s="47" t="inlineStr">
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="D105" s="43" t="n">
-        <v>23.249</v>
+        <v>15.685</v>
       </c>
       <c r="E105" s="44" t="inlineStr">
         <is>
@@ -6478,1500 +6478,21 @@
         <v>15</v>
       </c>
       <c r="H105" s="43" t="n">
-        <v>116.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I105" s="46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J105" s="46" t="n">
         <v>0</v>
       </c>
       <c r="K105" s="46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L105" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M105" s="46" t="n">
-        <v>170188</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="36" t="inlineStr">
-        <is>
-          <t>SRSR10100808-01</t>
-        </is>
-      </c>
-      <c r="B106" s="29" t="inlineStr">
-        <is>
-          <t>Batamaloo to Nasrullah Pora via Jehangir Chowk Rambagh Hyderpora</t>
-        </is>
-      </c>
-      <c r="C106" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D106" s="38" t="n">
-        <v>7.083</v>
-      </c>
-      <c r="E106" s="39" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F106" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G106" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H106" s="38" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="I106" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="J106" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="L106" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="41" t="n">
-        <v>33298</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="42" t="inlineStr">
-        <is>
-          <t>SRSR10100918</t>
-        </is>
-      </c>
-      <c r="B107" s="30" t="inlineStr">
-        <is>
-          <t>Batamaloo to Hazratbal via Khanyar</t>
-        </is>
-      </c>
-      <c r="C107" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D107" s="43" t="n">
-        <v>12.926</v>
-      </c>
-      <c r="E107" s="44" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F107" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G107" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H107" s="43" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="I107" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="J107" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="L107" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="46" t="n">
-        <v>98975</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="36" t="inlineStr">
-        <is>
-          <t>SRBG10020905</t>
-        </is>
-      </c>
-      <c r="B108" s="29" t="inlineStr">
-        <is>
-          <t>Batamaloo to Chadoora Chowk via Jehangir Chowk</t>
-        </is>
-      </c>
-      <c r="C108" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D108" s="38" t="n">
-        <v>10.858</v>
-      </c>
-      <c r="E108" s="39" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F108" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G108" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H108" s="38" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="I108" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="J108" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="L108" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="41" t="n">
-        <v>39417</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="42" t="inlineStr">
-        <is>
-          <t>SRSR10106039</t>
-        </is>
-      </c>
-      <c r="B109" s="30" t="inlineStr">
-        <is>
-          <t>LD Hospital to Pandach via Jehangir Chowk Dalgate Khanyar</t>
-        </is>
-      </c>
-      <c r="C109" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D109" s="43" t="n">
-        <v>10.884</v>
-      </c>
-      <c r="E109" s="44" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F109" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G109" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H109" s="43" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="I109" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="J109" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="L109" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="46" t="n">
-        <v>96645</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="36" t="inlineStr">
-        <is>
-          <t>SRBG10024017</t>
-        </is>
-      </c>
-      <c r="B110" s="29" t="inlineStr">
-        <is>
-          <t>Pantha Chowk to Narbal Crossing via Sonwar Jehangir Chowk Qamarwari</t>
-        </is>
-      </c>
-      <c r="C110" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D110" s="38" t="n">
-        <v>19.752</v>
-      </c>
-      <c r="E110" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F110" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G110" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H110" s="38" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="I110" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="J110" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="K110" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="L110" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="41" t="n">
-        <v>101613</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="42" t="inlineStr">
-        <is>
-          <t>SRPW10080908</t>
-        </is>
-      </c>
-      <c r="B111" s="30" t="inlineStr">
-        <is>
-          <t>Batamaloo to Drussu Pulwama via Marwal</t>
-        </is>
-      </c>
-      <c r="C111" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D111" s="49" t="n">
-        <v>32.735</v>
-      </c>
-      <c r="E111" s="44" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F111" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G111" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H111" s="43" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="I111" s="46" t="n">
-        <v>13</v>
-      </c>
-      <c r="J111" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="K111" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="L111" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="46" t="n">
-        <v>119785</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="36" t="inlineStr">
-        <is>
-          <t>SRBG10020904-01</t>
-        </is>
-      </c>
-      <c r="B112" s="29" t="inlineStr">
-        <is>
-          <t>Batamaloo to Budgam Railway Station via Khumeni Chowk</t>
-        </is>
-      </c>
-      <c r="C112" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D112" s="38" t="n">
-        <v>15.685</v>
-      </c>
-      <c r="E112" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F112" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G112" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H112" s="38" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="I112" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="J112" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="L112" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" s="41" t="n">
-        <v>46176</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="42" t="inlineStr">
-        <is>
-          <t>SRSR10105418</t>
-        </is>
-      </c>
-      <c r="B113" s="30" t="inlineStr">
-        <is>
-          <t>Parimpora to Naseem Bagh via Noorbagh Gojwara Mill Stop</t>
-        </is>
-      </c>
-      <c r="C113" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D113" s="43" t="n">
-        <v>15.058</v>
-      </c>
-      <c r="E113" s="44" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F113" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G113" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H113" s="43" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="I113" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="J113" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="L113" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="46" t="n">
-        <v>114293</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="36" t="inlineStr">
-        <is>
-          <t>SRBG10024005</t>
-        </is>
-      </c>
-      <c r="B114" s="29" t="inlineStr">
-        <is>
-          <t>Pantha Chowk to Agri Kalan Kanihama via Bypass</t>
-        </is>
-      </c>
-      <c r="C114" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D114" s="38" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="E114" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F114" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G114" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H114" s="38" t="n">
-        <v>118</v>
-      </c>
-      <c r="I114" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="J114" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="K114" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="L114" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="41" t="n">
-        <v>111959</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="42" t="inlineStr">
-        <is>
-          <t>SRSR10104242</t>
-        </is>
-      </c>
-      <c r="B115" s="30" t="inlineStr">
-        <is>
-          <t>Old City Loop Downtown Srinagar</t>
-        </is>
-      </c>
-      <c r="C115" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D115" s="43" t="n">
-        <v>1.169</v>
-      </c>
-      <c r="E115" s="44" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F115" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G115" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H115" s="43" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I115" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="J115" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L115" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="46" t="n">
-        <v>17652</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="36" t="inlineStr">
-        <is>
-          <t>BGSR02102451</t>
-        </is>
-      </c>
-      <c r="B116" s="29" t="inlineStr">
-        <is>
-          <t>Rangreth to District Court Srinagar via Barzulla Jehangir Chowk</t>
-        </is>
-      </c>
-      <c r="C116" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D116" s="38" t="n">
-        <v>10.327</v>
-      </c>
-      <c r="E116" s="39" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F116" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G116" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H116" s="38" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="I116" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="J116" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="L116" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="41" t="n">
-        <v>94458</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="42" t="inlineStr">
-        <is>
-          <t>SRGB10050904</t>
-        </is>
-      </c>
-      <c r="B117" s="30" t="inlineStr">
-        <is>
-          <t>Batamaloo to Beehama Ganderbal via Hazratbal Zakura</t>
-        </is>
-      </c>
-      <c r="C117" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D117" s="43" t="n">
-        <v>26.584</v>
-      </c>
-      <c r="E117" s="44" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F117" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G117" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H117" s="43" t="n">
-        <v>132.9</v>
-      </c>
-      <c r="I117" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="J117" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="L117" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="46" t="n">
-        <v>152128</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="36" t="inlineStr">
-        <is>
-          <t>SRGB10055204</t>
-        </is>
-      </c>
-      <c r="B118" s="29" t="inlineStr">
-        <is>
-          <t>TRC to Central University Ganderbal via Karan Nagar Zoonimar 90ft Road</t>
-        </is>
-      </c>
-      <c r="C118" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D118" s="38" t="n">
-        <v>27.314</v>
-      </c>
-      <c r="E118" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F118" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G118" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H118" s="38" t="n">
-        <v>136.6</v>
-      </c>
-      <c r="I118" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="J118" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="L118" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="41" t="n">
-        <v>125528</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="42" t="inlineStr">
-        <is>
-          <t>SRPW10085208</t>
-        </is>
-      </c>
-      <c r="B119" s="30" t="inlineStr">
-        <is>
-          <t>TRC to Pulwama via Nowgam Kaanipora</t>
-        </is>
-      </c>
-      <c r="C119" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D119" s="43" t="n">
-        <v>29.364</v>
-      </c>
-      <c r="E119" s="44" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F119" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G119" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H119" s="43" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="I119" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="J119" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="L119" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="46" t="n">
-        <v>127759</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="36" t="inlineStr">
-        <is>
-          <t>SRSR10100808-02</t>
-        </is>
-      </c>
-      <c r="B120" s="29" t="inlineStr">
-        <is>
-          <t>Batamaloo Circular via Khonmoh</t>
-        </is>
-      </c>
-      <c r="C120" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D120" s="38" t="n">
-        <v>13.87</v>
-      </c>
-      <c r="E120" s="39" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F120" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G120" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H120" s="38" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="I120" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="J120" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="L120" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="41" t="n">
-        <v>81554</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="42" t="inlineStr">
-        <is>
-          <t>SRAN10010902</t>
-        </is>
-      </c>
-      <c r="B121" s="30" t="inlineStr">
-        <is>
-          <t>Batamaloo to Womens College Batpora via Rainawari</t>
-        </is>
-      </c>
-      <c r="C121" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D121" s="43" t="n">
-        <v>4.508</v>
-      </c>
-      <c r="E121" s="44" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F121" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G121" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H121" s="43" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="I121" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="J121" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="L121" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="46" t="n">
-        <v>42363</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="36" t="inlineStr">
-        <is>
-          <t>SRBG10022505</t>
-        </is>
-      </c>
-      <c r="B122" s="29" t="inlineStr">
-        <is>
-          <t>Jkpdc Jehangir Chowk to Wadwan</t>
-        </is>
-      </c>
-      <c r="C122" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D122" s="38" t="n">
-        <v>15.202</v>
-      </c>
-      <c r="E122" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F122" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G122" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H122" s="38" t="n">
-        <v>76</v>
-      </c>
-      <c r="I122" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="J122" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="L122" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="41" t="n">
-        <v>87331</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="42" t="inlineStr">
-        <is>
-          <t>SRGB10054007</t>
-        </is>
-      </c>
-      <c r="B123" s="30" t="inlineStr">
-        <is>
-          <t>Pantha Chowk to Sumbal</t>
-        </is>
-      </c>
-      <c r="C123" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D123" s="49" t="n">
-        <v>35.736</v>
-      </c>
-      <c r="E123" s="44" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F123" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G123" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H123" s="43" t="n">
-        <v>178.7</v>
-      </c>
-      <c r="I123" s="46" t="n">
-        <v>14</v>
-      </c>
-      <c r="J123" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="K123" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="L123" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="46" t="n">
-        <v>119919</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="36" t="inlineStr">
-        <is>
-          <t>SRGB10054006</t>
-        </is>
-      </c>
-      <c r="B124" s="29" t="inlineStr">
-        <is>
-          <t>Pantha Chowk to Safapora</t>
-        </is>
-      </c>
-      <c r="C124" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D124" s="50" t="n">
-        <v>60.631</v>
-      </c>
-      <c r="E124" s="39" t="inlineStr">
-        <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F124" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G124" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H124" s="38" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="I124" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="J124" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="K124" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="L124" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="41" t="n">
-        <v>140491</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="42" t="inlineStr">
-        <is>
-          <t>SRBG10020802</t>
-        </is>
-      </c>
-      <c r="B125" s="30" t="inlineStr">
-        <is>
-          <t>Batamaloo to Arath</t>
-        </is>
-      </c>
-      <c r="C125" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D125" s="43" t="n">
-        <v>12.395</v>
-      </c>
-      <c r="E125" s="44" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F125" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G125" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H125" s="43" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="I125" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="J125" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="L125" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="46" t="n">
-        <v>73084</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="36" t="inlineStr">
-        <is>
-          <t>SRPW10080902</t>
-        </is>
-      </c>
-      <c r="B126" s="29" t="inlineStr">
-        <is>
-          <t>Batamaloo to Khrew Bus Stand</t>
-        </is>
-      </c>
-      <c r="C126" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D126" s="38" t="n">
-        <v>18.186</v>
-      </c>
-      <c r="E126" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F126" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G126" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H126" s="38" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="I126" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="J126" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="L126" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="41" t="n">
-        <v>97093</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="42" t="inlineStr">
-        <is>
-          <t>SRBG10020807</t>
-        </is>
-      </c>
-      <c r="B127" s="30" t="inlineStr">
-        <is>
-          <t>Batamaloo to Charesharief via Chadoora</t>
-        </is>
-      </c>
-      <c r="C127" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D127" s="43" t="n">
-        <v>29.633</v>
-      </c>
-      <c r="E127" s="44" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F127" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G127" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H127" s="43" t="n">
-        <v>148.2</v>
-      </c>
-      <c r="I127" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="J127" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="L127" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="46" t="n">
-        <v>115125</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="36" t="inlineStr">
-        <is>
-          <t>SRBR10044003</t>
-        </is>
-      </c>
-      <c r="B128" s="29" t="inlineStr">
-        <is>
-          <t>Pantha Chowk to Palhalan via Sangrama Sopore</t>
-        </is>
-      </c>
-      <c r="C128" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D128" s="50" t="n">
-        <v>36.463</v>
-      </c>
-      <c r="E128" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F128" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G128" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H128" s="38" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="I128" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="J128" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="K128" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="L128" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" s="41" t="n">
-        <v>131341</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="42" t="inlineStr">
-        <is>
-          <t>SRPW10080813</t>
-        </is>
-      </c>
-      <c r="B129" s="30" t="inlineStr">
-        <is>
-          <t>Batamaloo to Dadsara Tral via Awantipora</t>
-        </is>
-      </c>
-      <c r="C129" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D129" s="49" t="n">
-        <v>43.869</v>
-      </c>
-      <c r="E129" s="44" t="inlineStr">
-        <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F129" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G129" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H129" s="43" t="n">
-        <v>131.6</v>
-      </c>
-      <c r="I129" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="J129" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="L129" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" s="46" t="n">
-        <v>112839</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="36" t="inlineStr">
-        <is>
-          <t>SRGB10050804-01</t>
-        </is>
-      </c>
-      <c r="B130" s="29" t="inlineStr">
-        <is>
-          <t>Batamaloo to Kangan via Hazratbal Manigam</t>
-        </is>
-      </c>
-      <c r="C130" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D130" s="50" t="n">
-        <v>55.703</v>
-      </c>
-      <c r="E130" s="39" t="inlineStr">
-        <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F130" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G130" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H130" s="38" t="n">
-        <v>167.1</v>
-      </c>
-      <c r="I130" s="41" t="n">
-        <v>14</v>
-      </c>
-      <c r="J130" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="41" t="n">
-        <v>14</v>
-      </c>
-      <c r="L130" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="41" t="n">
-        <v>120242</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="42" t="inlineStr">
-        <is>
-          <t>SRGB10050804-02</t>
-        </is>
-      </c>
-      <c r="B131" s="30" t="inlineStr">
-        <is>
-          <t>Batamaloo to Manigam</t>
-        </is>
-      </c>
-      <c r="C131" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D131" s="49" t="n">
-        <v>54.466</v>
-      </c>
-      <c r="E131" s="44" t="inlineStr">
-        <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="F131" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G131" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H131" s="43" t="n">
-        <v>163.4</v>
-      </c>
-      <c r="I131" s="46" t="n">
-        <v>13</v>
-      </c>
-      <c r="J131" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="46" t="n">
-        <v>13</v>
-      </c>
-      <c r="L131" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" s="46" t="n">
-        <v>118108</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="36" t="inlineStr">
-        <is>
-          <t>SRPW10080905</t>
-        </is>
-      </c>
-      <c r="B132" s="29" t="inlineStr">
-        <is>
-          <t>Batamaloo to Pinglena Pampore via Galandar</t>
-        </is>
-      </c>
-      <c r="C132" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D132" s="38" t="n">
-        <v>22.233</v>
-      </c>
-      <c r="E132" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F132" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G132" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H132" s="38" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="I132" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="J132" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="K132" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="L132" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="41" t="n">
-        <v>108838</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="42" t="inlineStr">
-        <is>
-          <t>SRSR10104039</t>
-        </is>
-      </c>
-      <c r="B133" s="30" t="inlineStr">
-        <is>
-          <t>Pantha Chowk to Panzinara</t>
-        </is>
-      </c>
-      <c r="C133" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D133" s="43" t="n">
-        <v>10.811</v>
-      </c>
-      <c r="E133" s="44" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="F133" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G133" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H133" s="43" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="I133" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="J133" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="L133" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" s="46" t="n">
-        <v>65968</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="36" t="inlineStr">
-        <is>
-          <t>SRBG10020904-02</t>
-        </is>
-      </c>
-      <c r="B134" s="29" t="inlineStr">
-        <is>
-          <t>Batamaloo to Dc Office Budgam</t>
-        </is>
-      </c>
-      <c r="C134" s="47" t="inlineStr">
-        <is>
-          <t>Upgraded to Trunk</t>
-        </is>
-      </c>
-      <c r="D134" s="38" t="n">
-        <v>15.685</v>
-      </c>
-      <c r="E134" s="39" t="inlineStr">
-        <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="F134" s="40" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G134" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="H134" s="38" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="I134" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="J134" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="L134" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" s="41" t="n">
         <v>46176</v>
       </c>
     </row>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO_Pretty.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO_Pretty.xlsx
@@ -1297,7 +1297,7 @@
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102118</t>
+          <t>BGSR02102118A</t>
         </is>
       </c>
       <c r="B4" s="29" t="inlineStr">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>SRSR10101860-01</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B14" s="29" t="inlineStr">
@@ -2215,7 +2215,7 @@
     <row r="22">
       <c r="A22" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102140-01</t>
+          <t>BGSR02102140</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="40">
       <c r="A40" s="36" t="inlineStr">
         <is>
-          <t>SRSR10100840-01</t>
+          <t>SRSR10102507</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
@@ -3184,7 +3184,7 @@
     <row r="41">
       <c r="A41" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100840-02</t>
+          <t>SRSR10100840</t>
         </is>
       </c>
       <c r="B41" s="30" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="46">
       <c r="A46" s="36" t="inlineStr">
         <is>
-          <t>BGSR02102140-02</t>
+          <t>SRSR10101808</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="48">
       <c r="A48" s="36" t="inlineStr">
         <is>
-          <t>SRSR10101860-02</t>
+          <t>SRSR10102462</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
@@ -3592,7 +3592,7 @@
     <row r="49">
       <c r="A49" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100840-03</t>
+          <t>BGSR02102124</t>
         </is>
       </c>
       <c r="B49" s="30" t="inlineStr">
@@ -8488,7 +8488,7 @@
     <row r="145">
       <c r="A145" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100808-01</t>
+          <t>SRBG10020918</t>
         </is>
       </c>
       <c r="B145" s="30" t="inlineStr">
@@ -8692,7 +8692,7 @@
     <row r="149">
       <c r="A149" s="42" t="inlineStr">
         <is>
-          <t>SRBG10024017</t>
+          <t>SRBG10024017B</t>
         </is>
       </c>
       <c r="B149" s="30" t="inlineStr">
@@ -8794,7 +8794,7 @@
     <row r="151">
       <c r="A151" s="42" t="inlineStr">
         <is>
-          <t>SRBG10020904-01</t>
+          <t>SRBG10020904A</t>
         </is>
       </c>
       <c r="B151" s="30" t="inlineStr">
@@ -8845,7 +8845,7 @@
     <row r="152">
       <c r="A152" s="36" t="inlineStr">
         <is>
-          <t>SRSR10105418</t>
+          <t>BGSR02102118B</t>
         </is>
       </c>
       <c r="B152" s="29" t="inlineStr">
@@ -8896,7 +8896,7 @@
     <row r="153">
       <c r="A153" s="42" t="inlineStr">
         <is>
-          <t>SRBG10024005</t>
+          <t>SRBG10024017A</t>
         </is>
       </c>
       <c r="B153" s="30" t="inlineStr">
@@ -8947,7 +8947,7 @@
     <row r="154">
       <c r="A154" s="36" t="inlineStr">
         <is>
-          <t>SRSR10104242</t>
+          <t>SRSR10103761</t>
         </is>
       </c>
       <c r="B154" s="29" t="inlineStr">
@@ -9202,7 +9202,7 @@
     <row r="159">
       <c r="A159" s="42" t="inlineStr">
         <is>
-          <t>SRSR10100808-02</t>
+          <t>SRSR10100940</t>
         </is>
       </c>
       <c r="B159" s="30" t="inlineStr">
@@ -9304,7 +9304,7 @@
     <row r="161">
       <c r="A161" s="42" t="inlineStr">
         <is>
-          <t>SRBG10022505</t>
+          <t>SRSR10106005</t>
         </is>
       </c>
       <c r="B161" s="30" t="inlineStr">
@@ -9457,7 +9457,7 @@
     <row r="164">
       <c r="A164" s="36" t="inlineStr">
         <is>
-          <t>SRBG10020802</t>
+          <t>SRSR10100965</t>
         </is>
       </c>
       <c r="B164" s="29" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="166">
       <c r="A166" s="36" t="inlineStr">
         <is>
-          <t>SRBG10020807</t>
+          <t>SRBG10020907</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -9610,7 +9610,7 @@
     <row r="167">
       <c r="A167" s="42" t="inlineStr">
         <is>
-          <t>SRBR10044003</t>
+          <t>SRBR10044010</t>
         </is>
       </c>
       <c r="B167" s="30" t="inlineStr">
@@ -9661,7 +9661,7 @@
     <row r="168">
       <c r="A168" s="36" t="inlineStr">
         <is>
-          <t>SRPW10080813</t>
+          <t>SRPW10080913</t>
         </is>
       </c>
       <c r="B168" s="29" t="inlineStr">
@@ -9712,7 +9712,7 @@
     <row r="169">
       <c r="A169" s="42" t="inlineStr">
         <is>
-          <t>SRGB10050804-01</t>
+          <t>SRSR10100955A</t>
         </is>
       </c>
       <c r="B169" s="30" t="inlineStr">
@@ -9763,7 +9763,7 @@
     <row r="170">
       <c r="A170" s="36" t="inlineStr">
         <is>
-          <t>SRGB10050804-02</t>
+          <t>SRSR10100955B</t>
         </is>
       </c>
       <c r="B170" s="29" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="172">
       <c r="A172" s="36" t="inlineStr">
         <is>
-          <t>SRSR10104039</t>
+          <t>SRBG10024014</t>
         </is>
       </c>
       <c r="B172" s="29" t="inlineStr">
@@ -9916,7 +9916,7 @@
     <row r="173">
       <c r="A173" s="42" t="inlineStr">
         <is>
-          <t>SRBG10020904-02</t>
+          <t>SRBG10020904B</t>
         </is>
       </c>
       <c r="B173" s="30" t="inlineStr">
